--- a/Wykresy.xlsx
+++ b/Wykresy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\studia_aisd\algorytmy_sortowania\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC88F6B5-67F6-4149-BF96-555224820697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B39A61-5BAE-493F-86A2-C5805A103D6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{19E7D5CD-98A1-451F-9163-D7D48B512516}"/>
   </bookViews>
@@ -19,9 +19,6 @@
     <sheet name="MS" sheetId="4" r:id="rId4"/>
     <sheet name="QS" sheetId="5" r:id="rId5"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId6"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -32,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="9">
   <si>
     <t>RANDOM</t>
   </si>
@@ -54,13 +51,19 @@
   <si>
     <t>V SHAPE</t>
   </si>
+  <si>
+    <t>LAST</t>
+  </si>
+  <si>
+    <t>MIDDLE</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="171" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="0.00000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -103,8 +106,8 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -188,7 +191,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="pl-PL"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -3493,7 +3496,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>ASCENDING</c:v>
+                  <c:v>LAST</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3589,7 +3592,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>DESCENDING</c:v>
+                  <c:v>MIDDLE</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3673,198 +3676,6 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-368A-4447-9F1D-F10CFEFD7F11}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>QS!$K$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>FLAT</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>QS!$L$3:$L$17</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>QS!$K$3:$K$17</c:f>
-              <c:numCache>
-                <c:formatCode>0.00000</c:formatCode>
-                <c:ptCount val="15"/>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-368A-4447-9F1D-F10CFEFD7F11}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>QS!$N$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>V SHAPE</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>QS!$O$3:$O$17</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>QS!$N$3:$N$17</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-368A-4447-9F1D-F10CFEFD7F11}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7044,16 +6855,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>609599</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>552449</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7081,148 +6892,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Arkusz1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="1">
-          <cell r="B1" t="str">
-            <v>n</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3">
-            <v>1.2895630000002699E-2</v>
-          </cell>
-          <cell r="B3">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4">
-            <v>4.5536090000041399E-2</v>
-          </cell>
-          <cell r="B4">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5">
-            <v>0.10659839999998399</v>
-          </cell>
-          <cell r="B5">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6">
-            <v>0.17843498000002</v>
-          </cell>
-          <cell r="B6">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7">
-            <v>0.27907319000005298</v>
-          </cell>
-          <cell r="B7">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8">
-            <v>0.39907955999997202</v>
-          </cell>
-          <cell r="B8">
-            <v>6</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9">
-            <v>0.54504456000004198</v>
-          </cell>
-          <cell r="B9">
-            <v>7</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10">
-            <v>0.71580754000005897</v>
-          </cell>
-          <cell r="B10">
-            <v>8</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11">
-            <v>0.908800730000075</v>
-          </cell>
-          <cell r="B11">
-            <v>9</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12">
-            <v>1.1198589000000501</v>
-          </cell>
-          <cell r="B12">
-            <v>10</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13">
-            <v>1.35082415000006</v>
-          </cell>
-          <cell r="B13">
-            <v>11</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14">
-            <v>1.61096243000001</v>
-          </cell>
-          <cell r="B14">
-            <v>12</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15">
-            <v>1.89438412999998</v>
-          </cell>
-          <cell r="B15">
-            <v>13</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16">
-            <v>2.2099056500000098</v>
-          </cell>
-          <cell r="B16">
-            <v>14</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17">
-            <v>2.5968066699999302</v>
-          </cell>
-          <cell r="B17">
-            <v>15</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9399,23 +9068,19 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
-      <c r="K1" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-      <c r="N1" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
     <row r="2" spans="2:15" x14ac:dyDescent="0.25">
@@ -9438,18 +9103,10 @@
       <c r="I2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
@@ -9466,13 +9123,9 @@
         <v>1</v>
       </c>
       <c r="K3" s="3"/>
-      <c r="L3" s="1">
-        <v>1</v>
-      </c>
+      <c r="L3" s="1"/>
       <c r="N3" s="3"/>
-      <c r="O3" s="1">
-        <v>1</v>
-      </c>
+      <c r="O3" s="1"/>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
@@ -9492,15 +9145,9 @@
         <v>2</v>
       </c>
       <c r="K4" s="3"/>
-      <c r="L4" s="1">
-        <f>L3+1</f>
-        <v>2</v>
-      </c>
+      <c r="L4" s="1"/>
       <c r="N4" s="3"/>
-      <c r="O4" s="1">
-        <f>O3+1</f>
-        <v>2</v>
-      </c>
+      <c r="O4" s="1"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
@@ -9519,15 +9166,9 @@
         <v>3</v>
       </c>
       <c r="K5" s="3"/>
-      <c r="L5" s="1">
-        <f t="shared" ref="L5:L17" si="2">L4+1</f>
-        <v>3</v>
-      </c>
+      <c r="L5" s="1"/>
       <c r="N5" s="3"/>
-      <c r="O5" s="1">
-        <f t="shared" ref="O5:O17" si="3">O4+1</f>
-        <v>3</v>
-      </c>
+      <c r="O5" s="1"/>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B6" s="3"/>
@@ -9546,15 +9187,9 @@
         <v>4</v>
       </c>
       <c r="K6" s="3"/>
-      <c r="L6" s="1">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
+      <c r="L6" s="1"/>
       <c r="N6" s="3"/>
-      <c r="O6" s="1">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
+      <c r="O6" s="1"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B7" s="3"/>
@@ -9573,15 +9208,9 @@
         <v>5</v>
       </c>
       <c r="K7" s="3"/>
-      <c r="L7" s="1">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
+      <c r="L7" s="1"/>
       <c r="N7" s="3"/>
-      <c r="O7" s="1">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
+      <c r="O7" s="1"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B8" s="3"/>
@@ -9600,15 +9229,9 @@
         <v>6</v>
       </c>
       <c r="K8" s="3"/>
-      <c r="L8" s="1">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
+      <c r="L8" s="1"/>
       <c r="N8" s="3"/>
-      <c r="O8" s="1">
-        <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
+      <c r="O8" s="1"/>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" s="3"/>
@@ -9627,15 +9250,9 @@
         <v>7</v>
       </c>
       <c r="K9" s="3"/>
-      <c r="L9" s="1">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
+      <c r="L9" s="1"/>
       <c r="N9" s="3"/>
-      <c r="O9" s="1">
-        <f t="shared" si="3"/>
-        <v>7</v>
-      </c>
+      <c r="O9" s="1"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10" s="3"/>
@@ -9654,15 +9271,9 @@
         <v>8</v>
       </c>
       <c r="K10" s="3"/>
-      <c r="L10" s="1">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
+      <c r="L10" s="1"/>
       <c r="N10" s="3"/>
-      <c r="O10" s="1">
-        <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
+      <c r="O10" s="1"/>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B11" s="3"/>
@@ -9681,15 +9292,9 @@
         <v>9</v>
       </c>
       <c r="K11" s="3"/>
-      <c r="L11" s="1">
-        <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
+      <c r="L11" s="1"/>
       <c r="N11" s="3"/>
-      <c r="O11" s="1">
-        <f t="shared" si="3"/>
-        <v>9</v>
-      </c>
+      <c r="O11" s="1"/>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12" s="3"/>
@@ -9708,15 +9313,9 @@
         <v>10</v>
       </c>
       <c r="K12" s="3"/>
-      <c r="L12" s="1">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
+      <c r="L12" s="1"/>
       <c r="N12" s="3"/>
-      <c r="O12" s="1">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
+      <c r="O12" s="1"/>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B13" s="3"/>
@@ -9735,15 +9334,9 @@
         <v>11</v>
       </c>
       <c r="K13" s="3"/>
-      <c r="L13" s="1">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
+      <c r="L13" s="1"/>
       <c r="N13" s="3"/>
-      <c r="O13" s="1">
-        <f t="shared" si="3"/>
-        <v>11</v>
-      </c>
+      <c r="O13" s="1"/>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B14" s="3"/>
@@ -9762,15 +9355,9 @@
         <v>12</v>
       </c>
       <c r="K14" s="3"/>
-      <c r="L14" s="1">
-        <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
+      <c r="L14" s="1"/>
       <c r="N14" s="3"/>
-      <c r="O14" s="1">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
+      <c r="O14" s="1"/>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B15" s="3"/>
@@ -9789,15 +9376,9 @@
         <v>13</v>
       </c>
       <c r="K15" s="3"/>
-      <c r="L15" s="1">
-        <f t="shared" si="2"/>
-        <v>13</v>
-      </c>
+      <c r="L15" s="1"/>
       <c r="N15" s="3"/>
-      <c r="O15" s="1">
-        <f t="shared" si="3"/>
-        <v>13</v>
-      </c>
+      <c r="O15" s="1"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B16" s="3"/>
@@ -9816,15 +9397,9 @@
         <v>14</v>
       </c>
       <c r="K16" s="3"/>
-      <c r="L16" s="1">
-        <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
+      <c r="L16" s="1"/>
       <c r="N16" s="3"/>
-      <c r="O16" s="1">
-        <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
+      <c r="O16" s="1"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B17" s="3"/>
@@ -9844,15 +9419,9 @@
         <v>15</v>
       </c>
       <c r="K17" s="3"/>
-      <c r="L17" s="1">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
+      <c r="L17" s="1"/>
       <c r="N17" s="3"/>
-      <c r="O17" s="1">
-        <f t="shared" si="3"/>
-        <v>15</v>
-      </c>
+      <c r="O17" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Wykresy.xlsx
+++ b/Wykresy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\studia_aisd\algorytmy_sortowania\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B39A61-5BAE-493F-86A2-C5805A103D6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29D2C96D-AF92-4490-96D4-7495EB7A3C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{19E7D5CD-98A1-451F-9163-D7D48B512516}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{19E7D5CD-98A1-451F-9163-D7D48B512516}"/>
   </bookViews>
   <sheets>
     <sheet name="IS" sheetId="1" r:id="rId1"/>
@@ -281,49 +281,49 @@
                 </c:lvl>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>0,01290</c:v>
+                    <c:v>0,01203</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>0,04554</c:v>
+                    <c:v>0,04735</c:v>
                   </c:pt>
                   <c:pt idx="2">
-                    <c:v>0,10660</c:v>
+                    <c:v>0,10191</c:v>
                   </c:pt>
                   <c:pt idx="3">
-                    <c:v>0,17843</c:v>
+                    <c:v>0,17270</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>0,27907</c:v>
+                    <c:v>0,26500</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>0,39908</c:v>
+                    <c:v>0,38173</c:v>
                   </c:pt>
                   <c:pt idx="6">
-                    <c:v>0,54504</c:v>
+                    <c:v>0,51715</c:v>
                   </c:pt>
                   <c:pt idx="7">
-                    <c:v>0,71581</c:v>
+                    <c:v>0,67669</c:v>
                   </c:pt>
                   <c:pt idx="8">
-                    <c:v>0,90880</c:v>
+                    <c:v>0,85694</c:v>
                   </c:pt>
                   <c:pt idx="9">
-                    <c:v>1,11986</c:v>
+                    <c:v>1,05383</c:v>
                   </c:pt>
                   <c:pt idx="10">
-                    <c:v>1,35082</c:v>
+                    <c:v>1,29811</c:v>
                   </c:pt>
                   <c:pt idx="11">
-                    <c:v>1,61096</c:v>
+                    <c:v>1,52764</c:v>
                   </c:pt>
                   <c:pt idx="12">
-                    <c:v>1,89438</c:v>
+                    <c:v>1,79703</c:v>
                   </c:pt>
                   <c:pt idx="13">
-                    <c:v>2,20991</c:v>
+                    <c:v>2,07821</c:v>
                   </c:pt>
                   <c:pt idx="14">
-                    <c:v>2,59681</c:v>
+                    <c:v>2,37830</c:v>
                   </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
@@ -336,49 +336,49 @@
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.2895630000002699E-2</c:v>
+                  <c:v>1.2026800000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.5536090000041399E-2</c:v>
+                  <c:v>4.7352119999999297E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.10659839999998399</c:v>
+                  <c:v>0.101906809999996</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.17843498000002</c:v>
+                  <c:v>0.172704049999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.27907319000005298</c:v>
+                  <c:v>0.265004980000003</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.39907955999997202</c:v>
+                  <c:v>0.38173197000000397</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.54504456000004198</c:v>
+                  <c:v>0.51714583999999997</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.71580754000005897</c:v>
+                  <c:v>0.67668937000000196</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.908800730000075</c:v>
+                  <c:v>0.85694406999999695</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.1198589000000501</c:v>
+                  <c:v>1.0538272799999999</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.35082415000006</c:v>
+                  <c:v>1.29810537</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.61096243000001</c:v>
+                  <c:v>1.5276361599999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.89438412999998</c:v>
+                  <c:v>1.7970345999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.2099056500000098</c:v>
+                  <c:v>2.0782094199999999</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.5968066699999302</c:v>
+                  <c:v>2.3782967500000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -668,6 +668,51 @@
               <c:numCache>
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>1.0343999999804501E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.65920000000596E-4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.35649999996212E-4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.1811000000061499E-4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.1910999999904496E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.8400999999671503E-4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.6678000000260904E-4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.2078999999926E-4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7.0693000000119298E-4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7.9233999999814796E-4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9.5499000000245297E-4</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.4290000000114501E-4</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.01204999999708E-3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.09625999999707E-3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.17394000000103E-3</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -1096,57 +1141,106 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:xVal>
-            <c:strRef>
+            <c:multiLvlStrRef>
               <c:f>SS!$B$3:$C$17</c:f>
-              <c:strCache>
+              <c:multiLvlStrCache>
                 <c:ptCount val="15"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>7</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>8</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>9</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>10</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>11</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>12</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>13</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>14</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>15</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>0,01138</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>0,04442</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>0,09679</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>0,16176</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>0,25600</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>0,35798</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>0,49104</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>0,63820</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>0,81029</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>1,00392</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>1,21800</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>1,45096</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>1,70663</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>1,99174</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>2,43004</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
@@ -1154,6 +1248,51 @@
               <c:numCache>
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>1.13804100000038E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.4423310000001902E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.6786580000002606E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.161760220000007</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.25599808999999102</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.35797905999999102</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.49104384999999401</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.638195540000003</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.81029029999999602</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.00392338</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.2179960299999899</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.45096204999999</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.70663114</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.99173796</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.4300448299999902</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -1442,6 +1581,51 @@
               <c:numCache>
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>1.1810930000001401E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.5579520000001102E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.102432369999996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.17761743000000901</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.27528482000000098</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.39591920000000302</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.52693365999998598</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.69100402000001304</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.90792875999998102</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.1209079099999799</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.35179544999998</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.6097550999999799</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.88213537999999</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.1775392799999902</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.4898922799999998</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -1870,57 +2054,106 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:xVal>
-            <c:strRef>
+            <c:multiLvlStrRef>
               <c:f>HS!$B$3:$C$17</c:f>
-              <c:strCache>
+              <c:multiLvlStrCache>
                 <c:ptCount val="15"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>10</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>20</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>30</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>40</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>50</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>60</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>70</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>80</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>90</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>100</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>110</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>120</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>130</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>140</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>150</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>0,02104</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>0,04179</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>0,06579</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>0,08817</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>0,11055</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>0,13446</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>0,16153</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>0,18218</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>0,20557</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>0,23055</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>0,25660</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>0,28242</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>0,30764</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>0,33841</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>0,36236</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
@@ -1928,6 +2161,51 @@
               <c:numCache>
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>2.10359299999936E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.1789509999989601E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.5792329999999302E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.81689399999913E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.110551459999987</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.13445716000001001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.161532459999989</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.18217882999999799</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.205574060000003</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.23054614000000101</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.25660143000000002</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.28242096000001299</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.30764189999999803</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.33841027999999301</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.36235713000000902</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -2216,6 +2494,51 @@
               <c:numCache>
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>2.4259499999971E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.34314999999969E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.48232000000916E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.7847700000111203E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.1156970000001799E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.3060779999977901E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.5788879999990901E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.8133170000009999E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.0086530000003201E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.2269469999991999E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.4458189999995699E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.6438289999987302E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.8601709999998001E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.0908799999997402E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.32464599999866E-2</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -2338,6 +2661,8 @@
         <c:scaling>
           <c:logBase val="2"/>
           <c:orientation val="minMax"/>
+          <c:max val="16"/>
+          <c:min val="1"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -7249,7 +7574,7 @@
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B3" s="2">
-        <v>1.2895630000002699E-2</v>
+        <v>1.2026800000001E-2</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -7262,7 +7587,9 @@
       <c r="I3" s="1">
         <v>1</v>
       </c>
-      <c r="K3" s="3"/>
+      <c r="K3" s="3">
+        <v>1.0343999999804501E-4</v>
+      </c>
       <c r="L3" s="1">
         <v>1</v>
       </c>
@@ -7273,7 +7600,7 @@
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B4" s="2">
-        <v>4.5536090000041399E-2</v>
+        <v>4.7352119999999297E-2</v>
       </c>
       <c r="C4">
         <f>C3+1</f>
@@ -7289,7 +7616,9 @@
         <f>I3+1</f>
         <v>2</v>
       </c>
-      <c r="K4" s="3"/>
+      <c r="K4" s="3">
+        <v>1.65920000000596E-4</v>
+      </c>
       <c r="L4" s="1">
         <f>L3+1</f>
         <v>2</v>
@@ -7302,7 +7631,7 @@
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="2">
-        <v>0.10659839999998399</v>
+        <v>0.101906809999996</v>
       </c>
       <c r="C5">
         <f t="shared" ref="C5:C17" si="0">C4+1</f>
@@ -7317,7 +7646,9 @@
         <f t="shared" ref="I5:I17" si="1">I4+1</f>
         <v>3</v>
       </c>
-      <c r="K5" s="3"/>
+      <c r="K5" s="3">
+        <v>2.35649999996212E-4</v>
+      </c>
       <c r="L5" s="1">
         <f t="shared" ref="L5:L17" si="2">L4+1</f>
         <v>3</v>
@@ -7330,7 +7661,7 @@
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B6" s="2">
-        <v>0.17843498000002</v>
+        <v>0.172704049999998</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
@@ -7345,7 +7676,9 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="K6" s="3"/>
+      <c r="K6" s="3">
+        <v>3.1811000000061499E-4</v>
+      </c>
       <c r="L6" s="1">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -7358,7 +7691,7 @@
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B7" s="2">
-        <v>0.27907319000005298</v>
+        <v>0.265004980000003</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
@@ -7373,7 +7706,9 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="K7" s="3"/>
+      <c r="K7" s="3">
+        <v>5.1910999999904496E-4</v>
+      </c>
       <c r="L7" s="1">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -7386,7 +7721,7 @@
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B8" s="2">
-        <v>0.39907955999997202</v>
+        <v>0.38173197000000397</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
@@ -7401,7 +7736,9 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="K8" s="3"/>
+      <c r="K8" s="3">
+        <v>4.8400999999671503E-4</v>
+      </c>
       <c r="L8" s="1">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -7414,7 +7751,7 @@
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" s="2">
-        <v>0.54504456000004198</v>
+        <v>0.51714583999999997</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
@@ -7429,7 +7766,9 @@
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="K9" s="3"/>
+      <c r="K9" s="3">
+        <v>5.6678000000260904E-4</v>
+      </c>
       <c r="L9" s="1">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -7442,7 +7781,7 @@
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10" s="2">
-        <v>0.71580754000005897</v>
+        <v>0.67668937000000196</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
@@ -7457,7 +7796,9 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="K10" s="3"/>
+      <c r="K10" s="3">
+        <v>6.2078999999926E-4</v>
+      </c>
       <c r="L10" s="1">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -7470,7 +7811,7 @@
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B11" s="2">
-        <v>0.908800730000075</v>
+        <v>0.85694406999999695</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
@@ -7485,7 +7826,9 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="K11" s="3"/>
+      <c r="K11" s="3">
+        <v>7.0693000000119298E-4</v>
+      </c>
       <c r="L11" s="1">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -7498,7 +7841,7 @@
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12" s="2">
-        <v>1.1198589000000501</v>
+        <v>1.0538272799999999</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
@@ -7513,7 +7856,9 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="K12" s="3"/>
+      <c r="K12" s="3">
+        <v>7.9233999999814796E-4</v>
+      </c>
       <c r="L12" s="1">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -7526,7 +7871,7 @@
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B13" s="2">
-        <v>1.35082415000006</v>
+        <v>1.29810537</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
@@ -7541,7 +7886,9 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="K13" s="3"/>
+      <c r="K13" s="3">
+        <v>9.5499000000245297E-4</v>
+      </c>
       <c r="L13" s="1">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -7554,7 +7901,7 @@
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B14" s="2">
-        <v>1.61096243000001</v>
+        <v>1.5276361599999999</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
@@ -7569,7 +7916,9 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="K14" s="3"/>
+      <c r="K14" s="3">
+        <v>9.4290000000114501E-4</v>
+      </c>
       <c r="L14" s="1">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -7582,7 +7931,7 @@
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B15" s="2">
-        <v>1.89438412999998</v>
+        <v>1.7970345999999999</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
@@ -7597,7 +7946,9 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="K15" s="3"/>
+      <c r="K15" s="3">
+        <v>1.01204999999708E-3</v>
+      </c>
       <c r="L15" s="1">
         <f t="shared" si="2"/>
         <v>13</v>
@@ -7610,7 +7961,7 @@
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B16" s="2">
-        <v>2.2099056500000098</v>
+        <v>2.0782094199999999</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
@@ -7625,7 +7976,9 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="K16" s="3"/>
+      <c r="K16" s="3">
+        <v>1.09625999999707E-3</v>
+      </c>
       <c r="L16" s="1">
         <f t="shared" si="2"/>
         <v>14</v>
@@ -7638,7 +7991,7 @@
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B17" s="2">
-        <v>2.5968066699999302</v>
+        <v>2.3782967500000001</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
@@ -7654,7 +8007,9 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="K17" s="3"/>
+      <c r="K17" s="3">
+        <v>1.17394000000103E-3</v>
+      </c>
       <c r="L17" s="1">
         <f t="shared" si="2"/>
         <v>15</v>
@@ -7730,7 +8085,9 @@
       </c>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
+      <c r="B3" s="3">
+        <v>1.13804100000038E-2</v>
+      </c>
       <c r="C3">
         <v>1</v>
       </c>
@@ -7742,7 +8099,9 @@
       <c r="I3" s="1">
         <v>1</v>
       </c>
-      <c r="K3" s="3"/>
+      <c r="K3" s="3">
+        <v>1.1810930000001401E-2</v>
+      </c>
       <c r="L3" s="1">
         <v>1</v>
       </c>
@@ -7752,7 +8111,9 @@
       </c>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B4" s="3"/>
+      <c r="B4" s="3">
+        <v>4.4423310000001902E-2</v>
+      </c>
       <c r="C4">
         <f>C3+1</f>
         <v>2</v>
@@ -7767,7 +8128,9 @@
         <f>I3+1</f>
         <v>2</v>
       </c>
-      <c r="K4" s="3"/>
+      <c r="K4" s="3">
+        <v>4.5579520000001102E-2</v>
+      </c>
       <c r="L4" s="1">
         <f>L3+1</f>
         <v>2</v>
@@ -7779,7 +8142,9 @@
       </c>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B5" s="3"/>
+      <c r="B5" s="3">
+        <v>9.6786580000002606E-2</v>
+      </c>
       <c r="C5">
         <f t="shared" ref="C5:C17" si="0">C4+1</f>
         <v>3</v>
@@ -7793,7 +8158,9 @@
         <f t="shared" ref="I5:I17" si="1">I4+1</f>
         <v>3</v>
       </c>
-      <c r="K5" s="3"/>
+      <c r="K5" s="3">
+        <v>0.102432369999996</v>
+      </c>
       <c r="L5" s="1">
         <f t="shared" ref="L5:L17" si="2">L4+1</f>
         <v>3</v>
@@ -7805,7 +8172,9 @@
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B6" s="3"/>
+      <c r="B6" s="3">
+        <v>0.161760220000007</v>
+      </c>
       <c r="C6">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -7819,7 +8188,9 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="K6" s="3"/>
+      <c r="K6" s="3">
+        <v>0.17761743000000901</v>
+      </c>
       <c r="L6" s="1">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -7831,7 +8202,9 @@
       </c>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B7" s="3"/>
+      <c r="B7" s="3">
+        <v>0.25599808999999102</v>
+      </c>
       <c r="C7">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -7845,7 +8218,9 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="K7" s="3"/>
+      <c r="K7" s="3">
+        <v>0.27528482000000098</v>
+      </c>
       <c r="L7" s="1">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -7857,7 +8232,9 @@
       </c>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B8" s="3"/>
+      <c r="B8" s="3">
+        <v>0.35797905999999102</v>
+      </c>
       <c r="C8">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -7871,7 +8248,9 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="K8" s="3"/>
+      <c r="K8" s="3">
+        <v>0.39591920000000302</v>
+      </c>
       <c r="L8" s="1">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -7883,7 +8262,9 @@
       </c>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B9" s="3"/>
+      <c r="B9" s="3">
+        <v>0.49104384999999401</v>
+      </c>
       <c r="C9">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -7897,7 +8278,9 @@
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="K9" s="3"/>
+      <c r="K9" s="3">
+        <v>0.52693365999998598</v>
+      </c>
       <c r="L9" s="1">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -7909,7 +8292,9 @@
       </c>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B10" s="3"/>
+      <c r="B10" s="3">
+        <v>0.638195540000003</v>
+      </c>
       <c r="C10">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -7923,7 +8308,9 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="K10" s="3"/>
+      <c r="K10" s="3">
+        <v>0.69100402000001304</v>
+      </c>
       <c r="L10" s="1">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -7935,7 +8322,9 @@
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B11" s="3"/>
+      <c r="B11" s="3">
+        <v>0.81029029999999602</v>
+      </c>
       <c r="C11">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -7949,7 +8338,9 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="K11" s="3"/>
+      <c r="K11" s="3">
+        <v>0.90792875999998102</v>
+      </c>
       <c r="L11" s="1">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -7961,7 +8352,9 @@
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B12" s="3"/>
+      <c r="B12" s="3">
+        <v>1.00392338</v>
+      </c>
       <c r="C12">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -7975,7 +8368,9 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="K12" s="3"/>
+      <c r="K12" s="3">
+        <v>1.1209079099999799</v>
+      </c>
       <c r="L12" s="1">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -7987,7 +8382,9 @@
       </c>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B13" s="3"/>
+      <c r="B13" s="3">
+        <v>1.2179960299999899</v>
+      </c>
       <c r="C13">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -8001,7 +8398,9 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="K13" s="3"/>
+      <c r="K13" s="3">
+        <v>1.35179544999998</v>
+      </c>
       <c r="L13" s="1">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -8013,7 +8412,9 @@
       </c>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B14" s="3"/>
+      <c r="B14" s="3">
+        <v>1.45096204999999</v>
+      </c>
       <c r="C14">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -8027,7 +8428,9 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="K14" s="3"/>
+      <c r="K14" s="3">
+        <v>1.6097550999999799</v>
+      </c>
       <c r="L14" s="1">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -8039,7 +8442,9 @@
       </c>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B15" s="3"/>
+      <c r="B15" s="3">
+        <v>1.70663114</v>
+      </c>
       <c r="C15">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -8053,7 +8458,9 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="K15" s="3"/>
+      <c r="K15" s="3">
+        <v>1.88213537999999</v>
+      </c>
       <c r="L15" s="1">
         <f t="shared" si="2"/>
         <v>13</v>
@@ -8065,7 +8472,9 @@
       </c>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B16" s="3"/>
+      <c r="B16" s="3">
+        <v>1.99173796</v>
+      </c>
       <c r="C16">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -8079,7 +8488,9 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="K16" s="3"/>
+      <c r="K16" s="3">
+        <v>2.1775392799999902</v>
+      </c>
       <c r="L16" s="1">
         <f t="shared" si="2"/>
         <v>14</v>
@@ -8091,7 +8502,9 @@
       </c>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B17" s="3"/>
+      <c r="B17" s="3">
+        <v>2.4300448299999902</v>
+      </c>
       <c r="C17">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -8106,7 +8519,9 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="K17" s="3"/>
+      <c r="K17" s="3">
+        <v>2.4898922799999998</v>
+      </c>
       <c r="L17" s="1">
         <f t="shared" si="2"/>
         <v>15</v>
@@ -8182,9 +8597,11 @@
       </c>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
+      <c r="B3" s="3">
+        <v>2.10359299999936E-2</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3">
@@ -8194,7 +8611,9 @@
       <c r="I3" s="1">
         <v>1</v>
       </c>
-      <c r="K3" s="3"/>
+      <c r="K3" s="3">
+        <v>2.4259499999971E-3</v>
+      </c>
       <c r="L3" s="1">
         <v>1</v>
       </c>
@@ -8204,10 +8623,12 @@
       </c>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B4" s="3"/>
+      <c r="B4" s="3">
+        <v>4.1789509999989601E-2</v>
+      </c>
       <c r="C4">
-        <f>C3+1</f>
-        <v>2</v>
+        <f>C3+10^1</f>
+        <v>20</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4">
@@ -8219,7 +8640,9 @@
         <f>I3+1</f>
         <v>2</v>
       </c>
-      <c r="K4" s="3"/>
+      <c r="K4" s="3">
+        <v>4.34314999999969E-3</v>
+      </c>
       <c r="L4" s="1">
         <f>L3+1</f>
         <v>2</v>
@@ -8231,10 +8654,12 @@
       </c>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B5" s="3"/>
+      <c r="B5" s="3">
+        <v>6.5792329999999302E-2</v>
+      </c>
       <c r="C5">
-        <f t="shared" ref="C5:C17" si="0">C4+1</f>
-        <v>3</v>
+        <f t="shared" ref="C5:C17" si="0">C4+10^1</f>
+        <v>30</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5">
@@ -8245,7 +8670,9 @@
         <f t="shared" ref="I5:I17" si="1">I4+1</f>
         <v>3</v>
       </c>
-      <c r="K5" s="3"/>
+      <c r="K5" s="3">
+        <v>6.48232000000916E-3</v>
+      </c>
       <c r="L5" s="1">
         <f t="shared" ref="L5:L17" si="2">L4+1</f>
         <v>3</v>
@@ -8257,10 +8684,12 @@
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B6" s="3"/>
+      <c r="B6" s="3">
+        <v>8.81689399999913E-2</v>
+      </c>
       <c r="C6">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6">
@@ -8271,7 +8700,9 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="K6" s="3"/>
+      <c r="K6" s="3">
+        <v>8.7847700000111203E-3</v>
+      </c>
       <c r="L6" s="1">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -8283,10 +8714,12 @@
       </c>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B7" s="3"/>
+      <c r="B7" s="3">
+        <v>0.110551459999987</v>
+      </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7">
@@ -8297,7 +8730,9 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="K7" s="3"/>
+      <c r="K7" s="3">
+        <v>1.1156970000001799E-2</v>
+      </c>
       <c r="L7" s="1">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -8309,10 +8744,12 @@
       </c>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B8" s="3"/>
+      <c r="B8" s="3">
+        <v>0.13445716000001001</v>
+      </c>
       <c r="C8">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8">
@@ -8323,7 +8760,9 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="K8" s="3"/>
+      <c r="K8" s="3">
+        <v>1.3060779999977901E-2</v>
+      </c>
       <c r="L8" s="1">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -8335,10 +8774,12 @@
       </c>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B9" s="3"/>
+      <c r="B9" s="3">
+        <v>0.161532459999989</v>
+      </c>
       <c r="C9">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>70</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9">
@@ -8349,7 +8790,9 @@
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="K9" s="3"/>
+      <c r="K9" s="3">
+        <v>1.5788879999990901E-2</v>
+      </c>
       <c r="L9" s="1">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -8361,10 +8804,12 @@
       </c>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B10" s="3"/>
+      <c r="B10" s="3">
+        <v>0.18217882999999799</v>
+      </c>
       <c r="C10">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10">
@@ -8375,7 +8820,9 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="K10" s="3"/>
+      <c r="K10" s="3">
+        <v>1.8133170000009999E-2</v>
+      </c>
       <c r="L10" s="1">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -8387,10 +8834,12 @@
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B11" s="3"/>
+      <c r="B11" s="3">
+        <v>0.205574060000003</v>
+      </c>
       <c r="C11">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11">
@@ -8401,7 +8850,9 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="K11" s="3"/>
+      <c r="K11" s="3">
+        <v>2.0086530000003201E-2</v>
+      </c>
       <c r="L11" s="1">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -8413,10 +8864,12 @@
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B12" s="3"/>
+      <c r="B12" s="3">
+        <v>0.23054614000000101</v>
+      </c>
       <c r="C12">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12">
@@ -8427,7 +8880,9 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="K12" s="3"/>
+      <c r="K12" s="3">
+        <v>2.2269469999991999E-2</v>
+      </c>
       <c r="L12" s="1">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -8439,10 +8894,12 @@
       </c>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B13" s="3"/>
+      <c r="B13" s="3">
+        <v>0.25660143000000002</v>
+      </c>
       <c r="C13">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13">
@@ -8453,7 +8910,9 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="K13" s="3"/>
+      <c r="K13" s="3">
+        <v>2.4458189999995699E-2</v>
+      </c>
       <c r="L13" s="1">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -8465,10 +8924,12 @@
       </c>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B14" s="3"/>
+      <c r="B14" s="3">
+        <v>0.28242096000001299</v>
+      </c>
       <c r="C14">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14">
@@ -8479,7 +8940,9 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="K14" s="3"/>
+      <c r="K14" s="3">
+        <v>2.6438289999987302E-2</v>
+      </c>
       <c r="L14" s="1">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -8491,10 +8954,12 @@
       </c>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B15" s="3"/>
+      <c r="B15" s="3">
+        <v>0.30764189999999803</v>
+      </c>
       <c r="C15">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>130</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15">
@@ -8505,7 +8970,9 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="K15" s="3"/>
+      <c r="K15" s="3">
+        <v>2.8601709999998001E-2</v>
+      </c>
       <c r="L15" s="1">
         <f t="shared" si="2"/>
         <v>13</v>
@@ -8517,10 +8984,12 @@
       </c>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B16" s="3"/>
+      <c r="B16" s="3">
+        <v>0.33841027999999301</v>
+      </c>
       <c r="C16">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>140</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16">
@@ -8531,7 +9000,9 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="K16" s="3"/>
+      <c r="K16" s="3">
+        <v>3.0908799999997402E-2</v>
+      </c>
       <c r="L16" s="1">
         <f t="shared" si="2"/>
         <v>14</v>
@@ -8543,10 +9014,12 @@
       </c>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B17" s="3"/>
+      <c r="B17" s="3">
+        <v>0.36235713000000902</v>
+      </c>
       <c r="C17">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17">
@@ -8558,7 +9031,9 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="K17" s="3"/>
+      <c r="K17" s="3">
+        <v>3.32464599999866E-2</v>
+      </c>
       <c r="L17" s="1">
         <f t="shared" si="2"/>
         <v>15</v>

--- a/Wykresy.xlsx
+++ b/Wykresy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\studia_aisd\algorytmy_sortowania\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29D2C96D-AF92-4490-96D4-7495EB7A3C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1354E645-5E25-4E67-AC28-E93B744B3E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{19E7D5CD-98A1-451F-9163-D7D48B512516}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{19E7D5CD-98A1-451F-9163-D7D48B512516}"/>
   </bookViews>
   <sheets>
     <sheet name="IS" sheetId="1" r:id="rId1"/>
@@ -114,6 +114,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFC04DE"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -476,6 +481,51 @@
               <c:numCache>
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>3.2405000001745001E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.0988000002216703E-4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0198499999660199E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.36506999997436E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.6877099999874101E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.9887099999778002E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.3997400000098398E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.68952000001263E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.9708799999752901E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.3418200000141902E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.70965000001888E-3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.0137399999821298E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.4661199999609302E-3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4.6943299999838897E-3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.3557199999886501E-3</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -503,7 +553,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent3"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -572,6 +622,51 @@
               <c:numCache>
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>2.37475000003541E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.3164099999739805E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.21513779999986499</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.383297599999878</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.59812620000002403</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.85802510000030396</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.1713122000000999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.5260954999998799</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.9465801999999699</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.3870911999997499</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.82016909999993</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.3512731999999201</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.89625109999997</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4.5177859999998802</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.2451040000000804</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -615,49 +710,49 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>11</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>12</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>13</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>14</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>15</c:v>
+                  <c:v>18</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -669,49 +764,49 @@
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.0343999999804501E-4</c:v>
+                  <c:v>3.3773999994082202E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.65920000000596E-4</c:v>
+                  <c:v>4.1441000003032902E-4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.35649999996212E-4</c:v>
+                  <c:v>4.8261000001730199E-4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.1811000000061499E-4</c:v>
+                  <c:v>6.0788000000684401E-4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.1910999999904496E-4</c:v>
+                  <c:v>6.5556999998079798E-4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.8400999999671503E-4</c:v>
+                  <c:v>7.1244000000660805E-4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.6678000000260904E-4</c:v>
+                  <c:v>8.1143999996129395E-4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6.2078999999926E-4</c:v>
+                  <c:v>8.7516999992658302E-4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>7.0693000000119298E-4</c:v>
+                  <c:v>9.4318000001294402E-4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7.9233999999814796E-4</c:v>
+                  <c:v>9.8740999992514796E-4</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>9.5499000000245297E-4</c:v>
+                  <c:v>1.08957000002192E-3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>9.4290000000114501E-4</c:v>
+                  <c:v>1.2249800000063199E-3</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.01204999999708E-3</c:v>
+                  <c:v>1.2250200000380499E-3</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.09625999999707E-3</c:v>
+                  <c:v>1.47315000000162E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.17394000000103E-3</c:v>
+                  <c:v>1.5473400000701001E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -740,7 +835,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent5"/>
+                <a:schemeClr val="accent6"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -835,6 +930,7 @@
         <c:scaling>
           <c:logBase val="2"/>
           <c:orientation val="minMax"/>
+          <c:max val="20"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -1416,7 +1512,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent3"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1653,7 +1749,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent5"/>
+                <a:schemeClr val="accent6"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2302,6 +2398,51 @@
               <c:numCache>
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>2.27945099999942E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.7945899999967803E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.5582029999986797E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.102748380000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.12973804999996899</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.15872756000003299</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.185764670000025</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.21871406000000199</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.24616752000001699</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.27831538999998801</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.30960678000001202</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.33609983000001098</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.36545630000000501</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.39749246000001198</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.43321334000001999</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -2329,7 +2470,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent3"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2398,6 +2539,51 @@
               <c:numCache>
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>2.0781000000033599E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.7866199999998499E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.1616999999969205E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.8706680000031993E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.12213872999996001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.14884196999996599</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.17582784000001001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.20816297000001199</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.231503059999977</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.25898756000001399</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.29222389999999898</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.32404839999999202</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.34583521999998001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.37981147999998899</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.40501946999997901</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -2566,7 +2752,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent5"/>
+                <a:schemeClr val="accent6"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2635,6 +2821,51 @@
               <c:numCache>
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>1.9964449999997601E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.3409370000017503E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.7492769999989793E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.1893489999983993E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.116522420000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.144577089999984</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.170943110000007</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.198631120000027</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.22188695999998301</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.25193085999999298</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.28081431999999001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.30708472999999598</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.33498862000001201</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.365964450000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.39184334000001397</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -3150,7 +3381,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent3"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -3342,7 +3573,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent5"/>
+                <a:schemeClr val="accent6"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -3829,7 +4060,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:srgbClr val="00B050"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -3925,7 +4156,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent3"/>
+                <a:srgbClr val="FF0000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -7579,19 +7810,23 @@
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="E3" s="2"/>
+      <c r="E3" s="2">
+        <v>3.2405000001745001E-4</v>
+      </c>
       <c r="F3">
         <v>1</v>
       </c>
-      <c r="H3" s="3"/>
+      <c r="H3" s="3">
+        <v>2.37475000003541E-2</v>
+      </c>
       <c r="I3" s="1">
         <v>1</v>
       </c>
       <c r="K3" s="3">
-        <v>1.0343999999804501E-4</v>
+        <v>3.3773999994082202E-4</v>
       </c>
       <c r="L3" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N3" s="3"/>
       <c r="O3" s="1">
@@ -7606,22 +7841,26 @@
         <f>C3+1</f>
         <v>2</v>
       </c>
-      <c r="E4" s="2"/>
+      <c r="E4" s="2">
+        <v>7.0988000002216703E-4</v>
+      </c>
       <c r="F4">
         <f>F3+1</f>
         <v>2</v>
       </c>
-      <c r="H4" s="3"/>
+      <c r="H4" s="3">
+        <v>9.3164099999739805E-2</v>
+      </c>
       <c r="I4" s="1">
         <f>I3+1</f>
         <v>2</v>
       </c>
       <c r="K4" s="3">
-        <v>1.65920000000596E-4</v>
+        <v>4.1441000003032902E-4</v>
       </c>
       <c r="L4" s="1">
         <f>L3+1</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N4" s="3"/>
       <c r="O4" s="1">
@@ -7637,21 +7876,25 @@
         <f t="shared" ref="C5:C17" si="0">C4+1</f>
         <v>3</v>
       </c>
-      <c r="E5" s="2"/>
+      <c r="E5" s="2">
+        <v>1.0198499999660199E-3</v>
+      </c>
       <c r="F5">
         <v>3</v>
       </c>
-      <c r="H5" s="3"/>
+      <c r="H5" s="3">
+        <v>0.21513779999986499</v>
+      </c>
       <c r="I5" s="1">
         <f t="shared" ref="I5:I17" si="1">I4+1</f>
         <v>3</v>
       </c>
       <c r="K5" s="3">
-        <v>2.35649999996212E-4</v>
+        <v>4.8261000001730199E-4</v>
       </c>
       <c r="L5" s="1">
         <f t="shared" ref="L5:L17" si="2">L4+1</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N5" s="3"/>
       <c r="O5" s="1">
@@ -7667,21 +7910,25 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="E6" s="2"/>
+      <c r="E6" s="2">
+        <v>1.36506999997436E-3</v>
+      </c>
       <c r="F6">
         <v>4</v>
       </c>
-      <c r="H6" s="3"/>
+      <c r="H6" s="3">
+        <v>0.383297599999878</v>
+      </c>
       <c r="I6" s="1">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="K6" s="3">
-        <v>3.1811000000061499E-4</v>
+        <v>6.0788000000684401E-4</v>
       </c>
       <c r="L6" s="1">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N6" s="3"/>
       <c r="O6" s="1">
@@ -7697,21 +7944,25 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="E7" s="2"/>
+      <c r="E7" s="2">
+        <v>1.6877099999874101E-3</v>
+      </c>
       <c r="F7">
         <v>5</v>
       </c>
-      <c r="H7" s="3"/>
+      <c r="H7" s="3">
+        <v>0.59812620000002403</v>
+      </c>
       <c r="I7" s="1">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="K7" s="3">
-        <v>5.1910999999904496E-4</v>
+        <v>6.5556999998079798E-4</v>
       </c>
       <c r="L7" s="1">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N7" s="3"/>
       <c r="O7" s="1">
@@ -7727,21 +7978,25 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="E8" s="2"/>
+      <c r="E8" s="2">
+        <v>1.9887099999778002E-3</v>
+      </c>
       <c r="F8">
         <v>6</v>
       </c>
-      <c r="H8" s="3"/>
+      <c r="H8" s="3">
+        <v>0.85802510000030396</v>
+      </c>
       <c r="I8" s="1">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="K8" s="3">
-        <v>4.8400999999671503E-4</v>
+        <v>7.1244000000660805E-4</v>
       </c>
       <c r="L8" s="1">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N8" s="3"/>
       <c r="O8" s="1">
@@ -7757,21 +8012,25 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="E9" s="2"/>
+      <c r="E9" s="2">
+        <v>2.3997400000098398E-3</v>
+      </c>
       <c r="F9">
         <v>7</v>
       </c>
-      <c r="H9" s="3"/>
+      <c r="H9" s="3">
+        <v>1.1713122000000999</v>
+      </c>
       <c r="I9" s="1">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="K9" s="3">
-        <v>5.6678000000260904E-4</v>
+        <v>8.1143999996129395E-4</v>
       </c>
       <c r="L9" s="1">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N9" s="3"/>
       <c r="O9" s="1">
@@ -7787,21 +8046,25 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="E10" s="2"/>
+      <c r="E10" s="2">
+        <v>2.68952000001263E-3</v>
+      </c>
       <c r="F10">
         <v>8</v>
       </c>
-      <c r="H10" s="3"/>
+      <c r="H10" s="3">
+        <v>1.5260954999998799</v>
+      </c>
       <c r="I10" s="1">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="K10" s="3">
-        <v>6.2078999999926E-4</v>
+        <v>8.7516999992658302E-4</v>
       </c>
       <c r="L10" s="1">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N10" s="3"/>
       <c r="O10" s="1">
@@ -7817,21 +8080,25 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="E11" s="2"/>
+      <c r="E11" s="2">
+        <v>2.9708799999752901E-3</v>
+      </c>
       <c r="F11">
         <v>9</v>
       </c>
-      <c r="H11" s="3"/>
+      <c r="H11" s="3">
+        <v>1.9465801999999699</v>
+      </c>
       <c r="I11" s="1">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="K11" s="3">
-        <v>7.0693000000119298E-4</v>
+        <v>9.4318000001294402E-4</v>
       </c>
       <c r="L11" s="1">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N11" s="3"/>
       <c r="O11" s="1">
@@ -7847,21 +8114,25 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="E12" s="2"/>
+      <c r="E12" s="2">
+        <v>3.3418200000141902E-3</v>
+      </c>
       <c r="F12">
         <v>10</v>
       </c>
-      <c r="H12" s="3"/>
+      <c r="H12" s="3">
+        <v>2.3870911999997499</v>
+      </c>
       <c r="I12" s="1">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="K12" s="3">
-        <v>7.9233999999814796E-4</v>
+        <v>9.8740999992514796E-4</v>
       </c>
       <c r="L12" s="1">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N12" s="3"/>
       <c r="O12" s="1">
@@ -7877,21 +8148,25 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="E13" s="2"/>
+      <c r="E13" s="2">
+        <v>3.70965000001888E-3</v>
+      </c>
       <c r="F13">
         <v>11</v>
       </c>
-      <c r="H13" s="3"/>
+      <c r="H13" s="3">
+        <v>2.82016909999993</v>
+      </c>
       <c r="I13" s="1">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="K13" s="3">
-        <v>9.5499000000245297E-4</v>
+        <v>1.08957000002192E-3</v>
       </c>
       <c r="L13" s="1">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="N13" s="3"/>
       <c r="O13" s="1">
@@ -7907,21 +8182,25 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="E14" s="2"/>
+      <c r="E14" s="2">
+        <v>4.0137399999821298E-3</v>
+      </c>
       <c r="F14">
         <v>12</v>
       </c>
-      <c r="H14" s="3"/>
+      <c r="H14" s="3">
+        <v>3.3512731999999201</v>
+      </c>
       <c r="I14" s="1">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="K14" s="3">
-        <v>9.4290000000114501E-4</v>
+        <v>1.2249800000063199E-3</v>
       </c>
       <c r="L14" s="1">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N14" s="3"/>
       <c r="O14" s="1">
@@ -7937,21 +8216,25 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="E15" s="2"/>
+      <c r="E15" s="2">
+        <v>4.4661199999609302E-3</v>
+      </c>
       <c r="F15">
         <v>13</v>
       </c>
-      <c r="H15" s="3"/>
+      <c r="H15" s="3">
+        <v>3.89625109999997</v>
+      </c>
       <c r="I15" s="1">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="K15" s="3">
-        <v>1.01204999999708E-3</v>
+        <v>1.2250200000380499E-3</v>
       </c>
       <c r="L15" s="1">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N15" s="3"/>
       <c r="O15" s="1">
@@ -7967,21 +8250,25 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="E16" s="2"/>
+      <c r="E16" s="2">
+        <v>4.6943299999838897E-3</v>
+      </c>
       <c r="F16">
         <v>14</v>
       </c>
-      <c r="H16" s="3"/>
+      <c r="H16" s="3">
+        <v>4.5177859999998802</v>
+      </c>
       <c r="I16" s="1">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="K16" s="3">
-        <v>1.09625999999707E-3</v>
+        <v>1.47315000000162E-2</v>
       </c>
       <c r="L16" s="1">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N16" s="3"/>
       <c r="O16" s="1">
@@ -7997,22 +8284,26 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="E17" s="2"/>
+      <c r="E17" s="2">
+        <v>5.3557199999886501E-3</v>
+      </c>
       <c r="F17">
         <f>F16+1</f>
         <v>15</v>
       </c>
-      <c r="H17" s="3"/>
+      <c r="H17" s="3">
+        <v>5.2451040000000804</v>
+      </c>
       <c r="I17" s="1">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="K17" s="3">
-        <v>1.17394000000103E-3</v>
+        <v>1.5473400000701001E-3</v>
       </c>
       <c r="L17" s="1">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="N17" s="3"/>
       <c r="O17" s="1">
@@ -8603,11 +8894,15 @@
       <c r="C3">
         <v>10</v>
       </c>
-      <c r="E3" s="2"/>
+      <c r="E3" s="2">
+        <v>2.27945099999942E-2</v>
+      </c>
       <c r="F3">
         <v>1</v>
       </c>
-      <c r="H3" s="3"/>
+      <c r="H3" s="3">
+        <v>2.0781000000033599E-2</v>
+      </c>
       <c r="I3" s="1">
         <v>1</v>
       </c>
@@ -8617,7 +8912,9 @@
       <c r="L3" s="1">
         <v>1</v>
       </c>
-      <c r="N3" s="3"/>
+      <c r="N3" s="3">
+        <v>1.9964449999997601E-2</v>
+      </c>
       <c r="O3" s="1">
         <v>1</v>
       </c>
@@ -8630,12 +8927,16 @@
         <f>C3+10^1</f>
         <v>20</v>
       </c>
-      <c r="E4" s="2"/>
+      <c r="E4" s="2">
+        <v>4.7945899999967803E-2</v>
+      </c>
       <c r="F4">
         <f>F3+1</f>
         <v>2</v>
       </c>
-      <c r="H4" s="3"/>
+      <c r="H4" s="3">
+        <v>4.7866199999998499E-2</v>
+      </c>
       <c r="I4" s="1">
         <f>I3+1</f>
         <v>2</v>
@@ -8647,7 +8948,9 @@
         <f>L3+1</f>
         <v>2</v>
       </c>
-      <c r="N4" s="3"/>
+      <c r="N4" s="3">
+        <v>4.3409370000017503E-2</v>
+      </c>
       <c r="O4" s="1">
         <f>O3+1</f>
         <v>2</v>
@@ -8661,11 +8964,15 @@
         <f t="shared" ref="C5:C17" si="0">C4+10^1</f>
         <v>30</v>
       </c>
-      <c r="E5" s="2"/>
+      <c r="E5" s="2">
+        <v>7.5582029999986797E-2</v>
+      </c>
       <c r="F5">
         <v>3</v>
       </c>
-      <c r="H5" s="3"/>
+      <c r="H5" s="3">
+        <v>7.1616999999969205E-2</v>
+      </c>
       <c r="I5" s="1">
         <f t="shared" ref="I5:I17" si="1">I4+1</f>
         <v>3</v>
@@ -8677,7 +8984,9 @@
         <f t="shared" ref="L5:L17" si="2">L4+1</f>
         <v>3</v>
       </c>
-      <c r="N5" s="3"/>
+      <c r="N5" s="3">
+        <v>6.7492769999989793E-2</v>
+      </c>
       <c r="O5" s="1">
         <f t="shared" ref="O5:O17" si="3">O4+1</f>
         <v>3</v>
@@ -8691,11 +9000,15 @@
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="E6" s="2"/>
+      <c r="E6" s="2">
+        <v>0.102748380000002</v>
+      </c>
       <c r="F6">
         <v>4</v>
       </c>
-      <c r="H6" s="3"/>
+      <c r="H6" s="3">
+        <v>9.8706680000031993E-2</v>
+      </c>
       <c r="I6" s="1">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -8707,7 +9020,9 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="N6" s="3"/>
+      <c r="N6" s="3">
+        <v>9.1893489999983993E-2</v>
+      </c>
       <c r="O6" s="1">
         <f t="shared" si="3"/>
         <v>4</v>
@@ -8721,11 +9036,15 @@
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="E7" s="2"/>
+      <c r="E7" s="2">
+        <v>0.12973804999996899</v>
+      </c>
       <c r="F7">
         <v>5</v>
       </c>
-      <c r="H7" s="3"/>
+      <c r="H7" s="3">
+        <v>0.12213872999996001</v>
+      </c>
       <c r="I7" s="1">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -8737,7 +9056,9 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="N7" s="3"/>
+      <c r="N7" s="3">
+        <v>0.116522420000001</v>
+      </c>
       <c r="O7" s="1">
         <f t="shared" si="3"/>
         <v>5</v>
@@ -8751,11 +9072,15 @@
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="E8" s="2"/>
+      <c r="E8" s="2">
+        <v>0.15872756000003299</v>
+      </c>
       <c r="F8">
         <v>6</v>
       </c>
-      <c r="H8" s="3"/>
+      <c r="H8" s="3">
+        <v>0.14884196999996599</v>
+      </c>
       <c r="I8" s="1">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -8767,7 +9092,9 @@
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="N8" s="3"/>
+      <c r="N8" s="3">
+        <v>0.144577089999984</v>
+      </c>
       <c r="O8" s="1">
         <f t="shared" si="3"/>
         <v>6</v>
@@ -8781,11 +9108,15 @@
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="E9" s="2"/>
+      <c r="E9" s="2">
+        <v>0.185764670000025</v>
+      </c>
       <c r="F9">
         <v>7</v>
       </c>
-      <c r="H9" s="3"/>
+      <c r="H9" s="3">
+        <v>0.17582784000001001</v>
+      </c>
       <c r="I9" s="1">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -8797,7 +9128,9 @@
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="N9" s="3"/>
+      <c r="N9" s="3">
+        <v>0.170943110000007</v>
+      </c>
       <c r="O9" s="1">
         <f t="shared" si="3"/>
         <v>7</v>
@@ -8811,11 +9144,15 @@
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="E10" s="2"/>
+      <c r="E10" s="2">
+        <v>0.21871406000000199</v>
+      </c>
       <c r="F10">
         <v>8</v>
       </c>
-      <c r="H10" s="3"/>
+      <c r="H10" s="3">
+        <v>0.20816297000001199</v>
+      </c>
       <c r="I10" s="1">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -8827,7 +9164,9 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="N10" s="3"/>
+      <c r="N10" s="3">
+        <v>0.198631120000027</v>
+      </c>
       <c r="O10" s="1">
         <f t="shared" si="3"/>
         <v>8</v>
@@ -8841,11 +9180,15 @@
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="E11" s="2"/>
+      <c r="E11" s="2">
+        <v>0.24616752000001699</v>
+      </c>
       <c r="F11">
         <v>9</v>
       </c>
-      <c r="H11" s="3"/>
+      <c r="H11" s="3">
+        <v>0.231503059999977</v>
+      </c>
       <c r="I11" s="1">
         <f t="shared" si="1"/>
         <v>9</v>
@@ -8857,7 +9200,9 @@
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="N11" s="3"/>
+      <c r="N11" s="3">
+        <v>0.22188695999998301</v>
+      </c>
       <c r="O11" s="1">
         <f t="shared" si="3"/>
         <v>9</v>
@@ -8871,11 +9216,15 @@
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="E12" s="2"/>
+      <c r="E12" s="2">
+        <v>0.27831538999998801</v>
+      </c>
       <c r="F12">
         <v>10</v>
       </c>
-      <c r="H12" s="3"/>
+      <c r="H12" s="3">
+        <v>0.25898756000001399</v>
+      </c>
       <c r="I12" s="1">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -8887,7 +9236,9 @@
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="N12" s="3"/>
+      <c r="N12" s="3">
+        <v>0.25193085999999298</v>
+      </c>
       <c r="O12" s="1">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -8901,11 +9252,15 @@
         <f t="shared" si="0"/>
         <v>110</v>
       </c>
-      <c r="E13" s="2"/>
+      <c r="E13" s="2">
+        <v>0.30960678000001202</v>
+      </c>
       <c r="F13">
         <v>11</v>
       </c>
-      <c r="H13" s="3"/>
+      <c r="H13" s="3">
+        <v>0.29222389999999898</v>
+      </c>
       <c r="I13" s="1">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -8917,7 +9272,9 @@
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="N13" s="3"/>
+      <c r="N13" s="3">
+        <v>0.28081431999999001</v>
+      </c>
       <c r="O13" s="1">
         <f t="shared" si="3"/>
         <v>11</v>
@@ -8931,11 +9288,15 @@
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-      <c r="E14" s="2"/>
+      <c r="E14" s="2">
+        <v>0.33609983000001098</v>
+      </c>
       <c r="F14">
         <v>12</v>
       </c>
-      <c r="H14" s="3"/>
+      <c r="H14" s="3">
+        <v>0.32404839999999202</v>
+      </c>
       <c r="I14" s="1">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -8947,7 +9308,9 @@
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="N14" s="3"/>
+      <c r="N14" s="3">
+        <v>0.30708472999999598</v>
+      </c>
       <c r="O14" s="1">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -8961,11 +9324,15 @@
         <f t="shared" si="0"/>
         <v>130</v>
       </c>
-      <c r="E15" s="2"/>
+      <c r="E15" s="2">
+        <v>0.36545630000000501</v>
+      </c>
       <c r="F15">
         <v>13</v>
       </c>
-      <c r="H15" s="3"/>
+      <c r="H15" s="3">
+        <v>0.34583521999998001</v>
+      </c>
       <c r="I15" s="1">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -8977,7 +9344,9 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="N15" s="3"/>
+      <c r="N15" s="3">
+        <v>0.33498862000001201</v>
+      </c>
       <c r="O15" s="1">
         <f t="shared" si="3"/>
         <v>13</v>
@@ -8991,11 +9360,15 @@
         <f t="shared" si="0"/>
         <v>140</v>
       </c>
-      <c r="E16" s="2"/>
+      <c r="E16" s="2">
+        <v>0.39749246000001198</v>
+      </c>
       <c r="F16">
         <v>14</v>
       </c>
-      <c r="H16" s="3"/>
+      <c r="H16" s="3">
+        <v>0.37981147999998899</v>
+      </c>
       <c r="I16" s="1">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -9007,7 +9380,9 @@
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="N16" s="3"/>
+      <c r="N16" s="3">
+        <v>0.365964450000001</v>
+      </c>
       <c r="O16" s="1">
         <f t="shared" si="3"/>
         <v>14</v>
@@ -9021,12 +9396,16 @@
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-      <c r="E17" s="2"/>
+      <c r="E17" s="2">
+        <v>0.43321334000001999</v>
+      </c>
       <c r="F17">
         <f>F16+1</f>
         <v>15</v>
       </c>
-      <c r="H17" s="3"/>
+      <c r="H17" s="3">
+        <v>0.40501946999997901</v>
+      </c>
       <c r="I17" s="1">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -9038,7 +9417,9 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="N17" s="3"/>
+      <c r="N17" s="3">
+        <v>0.39184334000001397</v>
+      </c>
       <c r="O17" s="1">
         <f t="shared" si="3"/>
         <v>15</v>

--- a/Wykresy.xlsx
+++ b/Wykresy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\studia_aisd\algorytmy_sortowania\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1354E645-5E25-4E67-AC28-E93B744B3E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22F43043-C8AA-4722-96F9-E65B122C46EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{19E7D5CD-98A1-451F-9163-D7D48B512516}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{19E7D5CD-98A1-451F-9163-D7D48B512516}"/>
   </bookViews>
   <sheets>
     <sheet name="IS" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="9">
   <si>
     <t>RANDOM</t>
   </si>
@@ -62,8 +62,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.00000"/>
+    <numFmt numFmtId="169" formatCode="0.0000000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -103,11 +104,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -145,32 +150,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="pl-PL"/>
-              <a:t>IS</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -196,7 +175,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="pl-PL"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -223,7 +202,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="00B0F0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -233,157 +212,109 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:xVal>
-            <c:multiLvlStrRef>
-              <c:f>IS!$B$3:$C$17</c:f>
-              <c:multiLvlStrCache>
+            <c:numRef>
+              <c:f>IS!$A$2:$A$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>1</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>2</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>3</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>4</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>5</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>6</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>7</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>8</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>9</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>10</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>11</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>12</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>13</c:v>
-                  </c:pt>
-                  <c:pt idx="13">
-                    <c:v>14</c:v>
-                  </c:pt>
-                  <c:pt idx="14">
-                    <c:v>15</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>0,01203</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>0,04735</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>0,10191</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>0,17270</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>0,26500</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>0,38173</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>0,51715</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>0,67669</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>0,85694</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>1,05383</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>1,29811</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>1,52764</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>1,79703</c:v>
-                  </c:pt>
-                  <c:pt idx="13">
-                    <c:v>2,07821</c:v>
-                  </c:pt>
-                  <c:pt idx="14">
-                    <c:v>2,37830</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
+                <c:pt idx="0">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>12000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>13000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>14000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>16000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>17000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>18000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>19000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>IS!$B$3:$B$17</c:f>
+              <c:f>IS!$B$2:$B$16</c:f>
               <c:numCache>
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
-                <c:pt idx="0">
-                  <c:v>1.2026800000001E-2</c:v>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>0.30721069999981399</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.7352119999999297E-2</c:v>
+                  <c:v>0.45558799999980598</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.101906809999996</c:v>
+                  <c:v>0.60786150000012595</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.172704049999998</c:v>
+                  <c:v>0.77074999999967897</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.265004980000003</c:v>
+                  <c:v>0.961230200000045</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.38173197000000397</c:v>
+                  <c:v>1.1705431000000299</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.51714583999999997</c:v>
+                  <c:v>1.4176434000000799</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.67668937000000196</c:v>
+                  <c:v>1.76679779999994</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.85694406999999695</c:v>
+                  <c:v>1.9851642999997201</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.0538272799999999</c:v>
+                  <c:v>2.3113642999996902</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.29810537</c:v>
+                  <c:v>2.6444400999998798</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.5276361599999999</c:v>
+                  <c:v>3.0175906999998001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.7970345999999999</c:v>
+                  <c:v>3.3604879999997999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.0782094199999999</c:v>
+                  <c:v>3.8151886999998998</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.3782967500000001</c:v>
+                  <c:v>4.2824634999997198</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -391,7 +322,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A419-4BF4-AFAC-84A16503E0F3}"/>
+              <c16:uniqueId val="{00000000-0969-4D5F-A629-F0CBE8D274C5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -400,7 +331,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>IS!$E$1</c:f>
+              <c:f>IS!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -423,108 +354,108 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>IS!$F$3:$F$17</c:f>
+              <c:f>IS!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>6000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>7000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>8000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
+                  <c:v>9000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7</c:v>
+                  <c:v>11000</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8</c:v>
+                  <c:v>12000</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9</c:v>
+                  <c:v>13000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10</c:v>
+                  <c:v>14000</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>11</c:v>
+                  <c:v>15000</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>12</c:v>
+                  <c:v>16000</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>13</c:v>
+                  <c:v>17000</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>14</c:v>
+                  <c:v>18000</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>15</c:v>
+                  <c:v>19000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>IS!$E$3:$E$17</c:f>
+              <c:f>IS!$C$2:$C$16</c:f>
               <c:numCache>
-                <c:formatCode>0.00000</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>3.2405000001745001E-4</c:v>
+                  <c:v>1.54730000031122E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.0988000002216703E-4</c:v>
+                  <c:v>1.8291000001227E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0198499999660199E-3</c:v>
+                  <c:v>2.23740000001271E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.36506999997436E-3</c:v>
+                  <c:v>2.72189999986949E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.6877099999874101E-3</c:v>
+                  <c:v>3.0435000003308202E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.9887099999778002E-3</c:v>
+                  <c:v>3.38460000011764E-3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.3997400000098398E-3</c:v>
+                  <c:v>3.60510000018621E-3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.68952000001263E-3</c:v>
+                  <c:v>3.8497000000461399E-3</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.9708799999752901E-3</c:v>
+                  <c:v>4.3052999999417798E-3</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.3418200000141902E-3</c:v>
+                  <c:v>4.6677999998791997E-3</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.70965000001888E-3</c:v>
+                  <c:v>4.8817000001690697E-3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4.0137399999821298E-3</c:v>
+                  <c:v>5.7689999998729001E-3</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>4.4661199999609302E-3</c:v>
+                  <c:v>5.7770999997046601E-3</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>4.6943299999838897E-3</c:v>
+                  <c:v>6.0286999996606002E-3</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>5.3557199999886501E-3</c:v>
+                  <c:v>6.2232999998741399E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -532,7 +463,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-A419-4BF4-AFAC-84A16503E0F3}"/>
+              <c16:uniqueId val="{00000001-0969-4D5F-A629-F0CBE8D274C5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -541,11 +472,293 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>IS!$H$1</c:f>
+              <c:f>IS!$D$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>DESCENDING</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>IS!$A$2:$A$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>12000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>13000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>14000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>16000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>17000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>18000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>19000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>IS!$D$2:$D$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>0.57234600000037905</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.87804570000025695</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.13276829999995</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.42819370000006</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.8054827000000799</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.2503299999998401</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.7179971000000398</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.1981657000001098</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.7459339000001801</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.4209681000002004</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5.0299622999996201</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5.7007025000002596</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6.49658449999969</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>7.2027017999998799</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>8.0657694000001303</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-0969-4D5F-A629-F0CBE8D274C5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>IS!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>FLAT</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>IS!$A$2:$A$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>12000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>13000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>14000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>16000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>17000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>18000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>19000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>IS!$E$2:$E$16</c:f>
+              <c:numCache>
+                <c:formatCode>0.00000</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>3.9689999994152399E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.6110000039334398E-4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.3290000005290397E-4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.5750000021580404E-4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.1089999983087095E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.6600000011239899E-4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8.4030000016355102E-4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9.7079999977722699E-4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.17610000006607E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.0643999999047E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.2022999999317099E-3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.2292999999772201E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.3216000002103101E-3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.3784000002488E-3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.6263000002254501E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-0969-4D5F-A629-F0CBE8D274C5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>IS!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>V SHAPE</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -564,108 +777,108 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>IS!$I$3:$I$17</c:f>
+              <c:f>IS!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>6000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>7000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>8000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
+                  <c:v>9000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7</c:v>
+                  <c:v>11000</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8</c:v>
+                  <c:v>12000</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9</c:v>
+                  <c:v>13000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10</c:v>
+                  <c:v>14000</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>11</c:v>
+                  <c:v>15000</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>12</c:v>
+                  <c:v>16000</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>13</c:v>
+                  <c:v>17000</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>14</c:v>
+                  <c:v>18000</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>15</c:v>
+                  <c:v>19000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>IS!$H$3:$H$17</c:f>
+              <c:f>IS!$F$2:$F$16</c:f>
               <c:numCache>
-                <c:formatCode>0.00000</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>2.37475000003541E-2</c:v>
+                  <c:v>0.28953629999978098</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.3164099999739805E-2</c:v>
+                  <c:v>0.43907510000008099</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.21513779999986499</c:v>
+                  <c:v>0.60516770000003794</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.383297599999878</c:v>
+                  <c:v>0.76325990000032096</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.59812620000002403</c:v>
+                  <c:v>0.96820669999988196</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.85802510000030396</c:v>
+                  <c:v>1.15225519999967</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.1713122000000999</c:v>
+                  <c:v>1.4153353000001501</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.5260954999998799</c:v>
+                  <c:v>1.7971864999999501</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.9465801999999699</c:v>
+                  <c:v>1.9297953000000201</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.3870911999997499</c:v>
+                  <c:v>2.2352631999997299</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.82016909999993</c:v>
+                  <c:v>2.6419641000002199</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.3512731999999201</c:v>
+                  <c:v>3.1611447000000199</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.89625109999997</c:v>
+                  <c:v>3.58185110000022</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>4.5177859999998802</c:v>
+                  <c:v>3.97890750000033</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>5.2451040000000804</c:v>
+                  <c:v>4.4468391000000302</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -673,244 +886,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-A419-4BF4-AFAC-84A16503E0F3}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>IS!$K$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>FLAT</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>IS!$L$3:$L$17</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
-                <c:pt idx="0">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>18</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>IS!$K$3:$K$17</c:f>
-              <c:numCache>
-                <c:formatCode>0.00000</c:formatCode>
-                <c:ptCount val="15"/>
-                <c:pt idx="0">
-                  <c:v>3.3773999994082202E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.1441000003032902E-4</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4.8261000001730199E-4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6.0788000000684401E-4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>6.5556999998079798E-4</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>7.1244000000660805E-4</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>8.1143999996129395E-4</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8.7516999992658302E-4</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9.4318000001294402E-4</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>9.8740999992514796E-4</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1.08957000002192E-3</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1.2249800000063199E-3</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1.2250200000380499E-3</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1.47315000000162E-2</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1.5473400000701001E-3</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-A419-4BF4-AFAC-84A16503E0F3}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>IS!$N$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>V SHAPE</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>IS!$O$3:$O$17</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>IS!$N$3:$N$17</c:f>
-              <c:numCache>
-                <c:formatCode>0.00000</c:formatCode>
-                <c:ptCount val="15"/>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-A419-4BF4-AFAC-84A16503E0F3}"/>
+              <c16:uniqueId val="{00000004-0969-4D5F-A629-F0CBE8D274C5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -922,15 +898,16 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="723363720"/>
-        <c:axId val="723360120"/>
+        <c:axId val="840882696"/>
+        <c:axId val="840884496"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="723363720"/>
+        <c:axId val="840882696"/>
         <c:scaling>
           <c:logBase val="2"/>
           <c:orientation val="minMax"/>
-          <c:max val="20"/>
+          <c:max val="20000"/>
+          <c:min val="5000"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -948,7 +925,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="#,##0\K" sourceLinked="0"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -985,12 +962,12 @@
             <a:endParaRPr lang="pl-PL"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="723360120"/>
+        <c:crossAx val="840884496"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="723360120"/>
+        <c:axId val="840884496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1010,7 +987,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1047,10 +1024,9 @@
             <a:endParaRPr lang="pl-PL"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="723363720"/>
+        <c:crossAx val="840882696"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
-        <c:majorUnit val="0.2"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -1169,7 +1145,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="pl-PL"/>
+              <a:rPr lang="en-US"/>
               <a:t>SS</a:t>
             </a:r>
           </a:p>
@@ -1200,7 +1176,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="pl-PL"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1237,157 +1213,109 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:xVal>
-            <c:multiLvlStrRef>
-              <c:f>SS!$B$3:$C$17</c:f>
-              <c:multiLvlStrCache>
+            <c:numRef>
+              <c:f>SS!$A$2:$A$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>1</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>2</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>3</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>4</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>5</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>6</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>7</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>8</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>9</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>10</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>11</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>12</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>13</c:v>
-                  </c:pt>
-                  <c:pt idx="13">
-                    <c:v>14</c:v>
-                  </c:pt>
-                  <c:pt idx="14">
-                    <c:v>15</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>0,01138</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>0,04442</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>0,09679</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>0,16176</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>0,25600</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>0,35798</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>0,49104</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>0,63820</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>0,81029</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>1,00392</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>1,21800</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>1,45096</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>1,70663</c:v>
-                  </c:pt>
-                  <c:pt idx="13">
-                    <c:v>1,99174</c:v>
-                  </c:pt>
-                  <c:pt idx="14">
-                    <c:v>2,43004</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
+                <c:pt idx="0">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>12000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>13000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>14000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>16000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>17000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>18000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>19000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>SS!$B$3:$B$17</c:f>
+              <c:f>SS!$B$2:$B$16</c:f>
               <c:numCache>
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.13804100000038E-2</c:v>
+                  <c:v>0.29711640000004902</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.4423310000001902E-2</c:v>
+                  <c:v>0.42092019999972702</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.6786580000002606E-2</c:v>
+                  <c:v>0.56643490000033103</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.161760220000007</c:v>
+                  <c:v>0.689637999999831</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.25599808999999102</c:v>
+                  <c:v>0.93152640000016596</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.35797905999999102</c:v>
+                  <c:v>1.1448983999998701</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.49104384999999401</c:v>
+                  <c:v>1.2892377000002799</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.638195540000003</c:v>
+                  <c:v>1.6510609000001699</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.81029029999999602</c:v>
+                  <c:v>1.7719887000002901</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.00392338</c:v>
+                  <c:v>2.23256409999976</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.2179960299999899</c:v>
+                  <c:v>2.5738467999999499</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.45096204999999</c:v>
+                  <c:v>2.7353607000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.70663114</c:v>
+                  <c:v>3.3449150000001202</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.99173796</c:v>
+                  <c:v>3.40162020000025</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.4300448299999902</c:v>
+                  <c:v>4.11404940000011</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1395,7 +1323,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-B951-420D-8C3F-EFE5895A007B}"/>
+              <c16:uniqueId val="{00000000-DDE3-49A8-A840-7A9A7B9D6E93}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1404,7 +1332,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>SS!$E$1</c:f>
+              <c:f>SS!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1427,71 +1355,116 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>SS!$F$3:$F$17</c:f>
+              <c:f>SS!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>6000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>7000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>8000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
+                  <c:v>9000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7</c:v>
+                  <c:v>11000</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8</c:v>
+                  <c:v>12000</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9</c:v>
+                  <c:v>13000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10</c:v>
+                  <c:v>14000</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>11</c:v>
+                  <c:v>15000</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>12</c:v>
+                  <c:v>16000</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>13</c:v>
+                  <c:v>17000</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>14</c:v>
+                  <c:v>18000</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>15</c:v>
+                  <c:v>19000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>SS!$E$3:$E$17</c:f>
+              <c:f>SS!$C$2:$C$16</c:f>
               <c:numCache>
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>0.27801170000020597</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.39111229999980401</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.561001900000064</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.92349749999993902</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.86902899999995498</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.10183499999993</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.3148572000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.5503923000001101</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.8155158999998</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.7273538999997902</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.35320389999969</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.7455755999999298</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.0529510999999698</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.44943740000007</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.81637829999999</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-B951-420D-8C3F-EFE5895A007B}"/>
+              <c16:uniqueId val="{00000001-DDE3-49A8-A840-7A9A7B9D6E93}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1500,7 +1473,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>SS!$H$1</c:f>
+              <c:f>SS!$D$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1512,7 +1485,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="7030A0"/>
+                <a:schemeClr val="accent3"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1523,71 +1496,116 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>SS!$I$3:$I$17</c:f>
+              <c:f>SS!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>6000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>7000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>8000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
+                  <c:v>9000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7</c:v>
+                  <c:v>11000</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8</c:v>
+                  <c:v>12000</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9</c:v>
+                  <c:v>13000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10</c:v>
+                  <c:v>14000</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>11</c:v>
+                  <c:v>15000</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>12</c:v>
+                  <c:v>16000</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>13</c:v>
+                  <c:v>17000</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>14</c:v>
+                  <c:v>18000</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>15</c:v>
+                  <c:v>19000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>SS!$H$3:$H$17</c:f>
+              <c:f>SS!$D$2:$D$16</c:f>
               <c:numCache>
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>0.371550500000012</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.404069400000025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.56454829999984202</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.73407259999976304</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.92283070000030398</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.1276714999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.77930940000032</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.6312573999998601</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.89283960000011</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.1945440000004002</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.50375829999984</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.8445698000000399</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.2412036000000599</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.6253870999998901</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.1029728000003098</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-B951-420D-8C3F-EFE5895A007B}"/>
+              <c16:uniqueId val="{00000002-DDE3-49A8-A840-7A9A7B9D6E93}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1596,7 +1614,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>SS!$K$1</c:f>
+              <c:f>SS!$E$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1619,108 +1637,108 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>SS!$L$3:$L$17</c:f>
+              <c:f>SS!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>6000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>7000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>8000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
+                  <c:v>9000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7</c:v>
+                  <c:v>11000</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8</c:v>
+                  <c:v>12000</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9</c:v>
+                  <c:v>13000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10</c:v>
+                  <c:v>14000</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>11</c:v>
+                  <c:v>15000</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>12</c:v>
+                  <c:v>16000</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>13</c:v>
+                  <c:v>17000</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>14</c:v>
+                  <c:v>18000</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>15</c:v>
+                  <c:v>19000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>SS!$K$3:$K$17</c:f>
+              <c:f>SS!$E$2:$E$16</c:f>
               <c:numCache>
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.1810930000001401E-2</c:v>
+                  <c:v>0.26314849999971501</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.5579520000001102E-2</c:v>
+                  <c:v>0.37396750000016199</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.102432369999996</c:v>
+                  <c:v>0.529808199999934</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.17761743000000901</c:v>
+                  <c:v>0.71018950000006897</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.27528482000000098</c:v>
+                  <c:v>0.84070620000011298</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.39591920000000302</c:v>
+                  <c:v>1.0199678999997499</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.52693365999998598</c:v>
+                  <c:v>1.24446809999972</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.69100402000001304</c:v>
+                  <c:v>1.49062700000013</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.90792875999998102</c:v>
+                  <c:v>1.77890509999997</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.1209079099999799</c:v>
+                  <c:v>2.02817709999999</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.35179544999998</c:v>
+                  <c:v>2.3299543999996701</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.6097550999999799</c:v>
+                  <c:v>2.6098971999999701</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.88213537999999</c:v>
+                  <c:v>2.99417149999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.1775392799999902</c:v>
+                  <c:v>3.33117489999995</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.4898922799999998</c:v>
+                  <c:v>3.7084792000000499</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1728,7 +1746,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-B951-420D-8C3F-EFE5895A007B}"/>
+              <c16:uniqueId val="{00000003-DDE3-49A8-A840-7A9A7B9D6E93}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1737,7 +1755,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>SS!$N$1</c:f>
+              <c:f>SS!$F$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1749,7 +1767,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent6"/>
+                <a:schemeClr val="accent5"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1760,71 +1778,116 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>SS!$O$3:$O$17</c:f>
+              <c:f>SS!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>6000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>7000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>8000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
+                  <c:v>9000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7</c:v>
+                  <c:v>11000</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8</c:v>
+                  <c:v>12000</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9</c:v>
+                  <c:v>13000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10</c:v>
+                  <c:v>14000</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>11</c:v>
+                  <c:v>15000</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>12</c:v>
+                  <c:v>16000</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>13</c:v>
+                  <c:v>17000</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>14</c:v>
+                  <c:v>18000</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>15</c:v>
+                  <c:v>19000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>SS!$N$3:$N$17</c:f>
+              <c:f>SS!$F$2:$F$16</c:f>
               <c:numCache>
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>0.29711640000004902</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.42092019999972702</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.56643490000033103</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.689637999999831</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.93152640000016596</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.1448983999998701</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.2892377000002799</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.6510609000001699</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.7719887000002901</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.23256409999976</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.5738467999999499</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.7353607000000002</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.3449150000001202</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.40162020000025</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.11404940000011</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-B951-420D-8C3F-EFE5895A007B}"/>
+              <c16:uniqueId val="{00000004-DDE3-49A8-A840-7A9A7B9D6E93}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1836,14 +1899,16 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="723363720"/>
-        <c:axId val="723360120"/>
+        <c:axId val="850038512"/>
+        <c:axId val="850036352"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="723363720"/>
+        <c:axId val="850038512"/>
         <c:scaling>
           <c:logBase val="2"/>
           <c:orientation val="minMax"/>
+          <c:max val="20000"/>
+          <c:min val="5000"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -1861,7 +1926,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="#,##0\K" sourceLinked="0"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1898,12 +1963,12 @@
             <a:endParaRPr lang="pl-PL"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="723360120"/>
+        <c:crossAx val="850036352"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="723360120"/>
+        <c:axId val="850036352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1923,7 +1988,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+        <c:numFmt formatCode="0.00000" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1960,10 +2025,9 @@
             <a:endParaRPr lang="pl-PL"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="723363720"/>
+        <c:crossAx val="850038512"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
-        <c:majorUnit val="0.2"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -2113,7 +2177,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="pl-PL"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -2140,7 +2204,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="00B0F0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2150,110 +2214,62 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:xVal>
-            <c:multiLvlStrRef>
-              <c:f>HS!$B$3:$C$17</c:f>
-              <c:multiLvlStrCache>
+            <c:numRef>
+              <c:f>HS!$A$2:$A$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>10</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>20</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>30</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>40</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>50</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>60</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>70</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>80</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>90</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>100</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>110</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>120</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>130</c:v>
-                  </c:pt>
-                  <c:pt idx="13">
-                    <c:v>140</c:v>
-                  </c:pt>
-                  <c:pt idx="14">
-                    <c:v>150</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>0,02104</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>0,04179</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>0,06579</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>0,08817</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>0,11055</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>0,13446</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>0,16153</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>0,18218</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>0,20557</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>0,23055</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>0,25660</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>0,28242</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>0,30764</c:v>
-                  </c:pt>
-                  <c:pt idx="13">
-                    <c:v>0,33841</c:v>
-                  </c:pt>
-                  <c:pt idx="14">
-                    <c:v>0,36236</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
+                <c:pt idx="0">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>60000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>70000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>80000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>90000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>110000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>120000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>130000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>140000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>150000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>HS!$B$3:$B$17</c:f>
+              <c:f>HS!$B$2:$B$16</c:f>
               <c:numCache>
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
@@ -2308,7 +2324,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D275-40A5-8CC2-772B3D186F8E}"/>
+              <c16:uniqueId val="{00000000-6C18-4AB7-874A-8623EB59C5AB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2317,7 +2333,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>HS!$E$1</c:f>
+              <c:f>HS!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2340,61 +2356,61 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>HS!$F$3:$F$17</c:f>
+              <c:f>HS!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>20000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>30000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>40000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6</c:v>
+                  <c:v>60000</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7</c:v>
+                  <c:v>70000</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8</c:v>
+                  <c:v>80000</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9</c:v>
+                  <c:v>90000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>11</c:v>
+                  <c:v>110000</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>12</c:v>
+                  <c:v>120000</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>13</c:v>
+                  <c:v>130000</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>14</c:v>
+                  <c:v>140000</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>15</c:v>
+                  <c:v>150000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>HS!$E$3:$E$17</c:f>
+              <c:f>HS!$C$2:$C$16</c:f>
               <c:numCache>
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
@@ -2449,7 +2465,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-D275-40A5-8CC2-772B3D186F8E}"/>
+              <c16:uniqueId val="{00000001-6C18-4AB7-874A-8623EB59C5AB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2458,11 +2474,293 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>HS!$H$1</c:f>
+              <c:f>HS!$D$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>DESCENDING</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>HS!$A$2:$A$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>60000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>70000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>80000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>90000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>110000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>120000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>130000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>140000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>150000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>HS!$D$2:$D$16</c:f>
+              <c:numCache>
+                <c:formatCode>0.00000</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>2.0781000000033599E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.7866199999998499E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.1616999999969205E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.8706680000031993E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.12213872999996001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.14884196999996599</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.17582784000001001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.20816297000001199</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.231503059999977</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.25898756000001399</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.29222389999999898</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.32404839999999202</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.34583521999998001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.37981147999998899</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.40501946999997901</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-6C18-4AB7-874A-8623EB59C5AB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>HS!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>FLAT</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>HS!$A$2:$A$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>60000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>70000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>80000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>90000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>110000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>120000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>130000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>140000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>150000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>HS!$E$2:$E$16</c:f>
+              <c:numCache>
+                <c:formatCode>0.00000</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>2.4259499999971E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.34314999999969E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.48232000000916E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.7847700000111203E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.1156970000001799E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.3060779999977901E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.5788879999990901E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.8133170000009999E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.0086530000003201E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.2269469999991999E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.4458189999995699E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.6438289999987302E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.8601709999998001E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.0908799999997402E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.32464599999866E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-6C18-4AB7-874A-8623EB59C5AB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>HS!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>V SHAPE</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2481,108 +2779,108 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>HS!$I$3:$I$17</c:f>
+              <c:f>HS!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>20000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>30000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>40000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6</c:v>
+                  <c:v>60000</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7</c:v>
+                  <c:v>70000</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8</c:v>
+                  <c:v>80000</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9</c:v>
+                  <c:v>90000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>11</c:v>
+                  <c:v>110000</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>12</c:v>
+                  <c:v>120000</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>13</c:v>
+                  <c:v>130000</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>14</c:v>
+                  <c:v>140000</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>15</c:v>
+                  <c:v>150000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>HS!$H$3:$H$17</c:f>
+              <c:f>HS!$F$2:$F$16</c:f>
               <c:numCache>
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>2.0781000000033599E-2</c:v>
+                  <c:v>1.9964449999997601E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.7866199999998499E-2</c:v>
+                  <c:v>4.3409370000017503E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.1616999999969205E-2</c:v>
+                  <c:v>6.7492769999989793E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.8706680000031993E-2</c:v>
+                  <c:v>9.1893489999983993E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.12213872999996001</c:v>
+                  <c:v>0.116522420000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.14884196999996599</c:v>
+                  <c:v>0.144577089999984</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.17582784000001001</c:v>
+                  <c:v>0.170943110000007</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.20816297000001199</c:v>
+                  <c:v>0.198631120000027</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.231503059999977</c:v>
+                  <c:v>0.22188695999998301</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.25898756000001399</c:v>
+                  <c:v>0.25193085999999298</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.29222389999999898</c:v>
+                  <c:v>0.28081431999999001</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.32404839999999202</c:v>
+                  <c:v>0.30708472999999598</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.34583521999998001</c:v>
+                  <c:v>0.33498862000001201</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.37981147999998899</c:v>
+                  <c:v>0.365964450000001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.40501946999997901</c:v>
+                  <c:v>0.39184334000001397</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2590,289 +2888,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-D275-40A5-8CC2-772B3D186F8E}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>HS!$K$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>FLAT</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>HS!$L$3:$L$17</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>HS!$K$3:$K$17</c:f>
-              <c:numCache>
-                <c:formatCode>0.00000</c:formatCode>
-                <c:ptCount val="15"/>
-                <c:pt idx="0">
-                  <c:v>2.4259499999971E-3</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.34314999999969E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>6.48232000000916E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>8.7847700000111203E-3</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.1156970000001799E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1.3060779999977901E-2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1.5788879999990901E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1.8133170000009999E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>2.0086530000003201E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2.2269469999991999E-2</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>2.4458189999995699E-2</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>2.6438289999987302E-2</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>2.8601709999998001E-2</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>3.0908799999997402E-2</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>3.32464599999866E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-D275-40A5-8CC2-772B3D186F8E}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>HS!$N$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>V SHAPE</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>HS!$O$3:$O$17</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>HS!$N$3:$N$17</c:f>
-              <c:numCache>
-                <c:formatCode>0.00000</c:formatCode>
-                <c:ptCount val="15"/>
-                <c:pt idx="0">
-                  <c:v>1.9964449999997601E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.3409370000017503E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>6.7492769999989793E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>9.1893489999983993E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.116522420000001</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.144577089999984</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.170943110000007</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.198631120000027</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.22188695999998301</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.25193085999999298</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.28081431999999001</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.30708472999999598</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.33498862000001201</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.365964450000001</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.39184334000001397</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-D275-40A5-8CC2-772B3D186F8E}"/>
+              <c16:uniqueId val="{00000004-6C18-4AB7-874A-8623EB59C5AB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2884,16 +2900,16 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="723363720"/>
-        <c:axId val="723360120"/>
+        <c:axId val="837845144"/>
+        <c:axId val="837841544"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="723363720"/>
+        <c:axId val="837845144"/>
         <c:scaling>
           <c:logBase val="2"/>
           <c:orientation val="minMax"/>
-          <c:max val="16"/>
-          <c:min val="1"/>
+          <c:max val="160000"/>
+          <c:min val="10000"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -2911,7 +2927,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="#,##0\K" sourceLinked="0"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2948,12 +2964,12 @@
             <a:endParaRPr lang="pl-PL"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="723360120"/>
+        <c:crossAx val="837841544"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="723360120"/>
+        <c:axId val="837841544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2973,7 +2989,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+        <c:numFmt formatCode="0.00000" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3010,10 +3026,9 @@
             <a:endParaRPr lang="pl-PL"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="723363720"/>
+        <c:crossAx val="837845144"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
-        <c:majorUnit val="0.2"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -3163,7 +3178,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="pl-PL"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -3190,7 +3205,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="00B0F0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -3200,71 +3215,117 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:xVal>
-            <c:strRef>
-              <c:f>MS!$B$3:$C$17</c:f>
-              <c:strCache>
+            <c:numRef>
+              <c:f>MS!$A$2:$A$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>20000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>30000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>40000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6</c:v>
+                  <c:v>60000</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7</c:v>
+                  <c:v>70000</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8</c:v>
+                  <c:v>80000</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9</c:v>
+                  <c:v>90000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>11</c:v>
+                  <c:v>110000</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>12</c:v>
+                  <c:v>120000</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>13</c:v>
+                  <c:v>130000</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>14</c:v>
+                  <c:v>140000</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+                  <c:v>150000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>MS!$B$3:$B$17</c:f>
+              <c:f>MS!$B$2:$B$16</c:f>
               <c:numCache>
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>2.0019500000034801E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.1490420000036402E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.4305039999999203E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.6936269999978305E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.108763700000008</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.13077272000000401</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.15336612999999399</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.17732276000001501</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.20086420999996299</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.224657350000006</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.24952613999998899</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.27439481999999699</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.29654835000001101</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.32133721999998599</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.346233530000017</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-72E2-47EE-9E7F-E08A698202E6}"/>
+              <c16:uniqueId val="{00000000-8F23-43BC-9E7A-09DB3455A3DB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3273,7 +3334,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>MS!$E$1</c:f>
+              <c:f>MS!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3296,71 +3357,116 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>MS!$F$3:$F$17</c:f>
+              <c:f>MS!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>20000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>30000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>40000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6</c:v>
+                  <c:v>60000</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7</c:v>
+                  <c:v>70000</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8</c:v>
+                  <c:v>80000</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9</c:v>
+                  <c:v>90000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>11</c:v>
+                  <c:v>110000</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>12</c:v>
+                  <c:v>120000</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>13</c:v>
+                  <c:v>130000</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>14</c:v>
+                  <c:v>140000</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>15</c:v>
+                  <c:v>150000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>MS!$E$3:$E$17</c:f>
+              <c:f>MS!$C$2:$C$16</c:f>
               <c:numCache>
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>1.7841350000025999E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.7062779999996499E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.86902699999882E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.0023600000003997E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.9360209999986099E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.119507720000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.14486256999998601</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.162076529999967</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.18628506999998501</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.20845273999998401</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.22946242999996599</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.24798472999996099</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.26957318999998198</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.29025454000002299</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.31542898000002401</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-72E2-47EE-9E7F-E08A698202E6}"/>
+              <c16:uniqueId val="{00000001-8F23-43BC-9E7A-09DB3455A3DB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3369,11 +3475,293 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>MS!$H$1</c:f>
+              <c:f>MS!$D$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>DESCENDING</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>MS!$A$2:$A$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>60000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>70000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>80000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>90000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>110000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>120000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>130000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>140000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>150000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>MS!$D$2:$D$16</c:f>
+              <c:numCache>
+                <c:formatCode>0.00000</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>1.8160039999975099E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.73390899999776E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.8605320000015101E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.9978059999984905E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.9421810000012503E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.12010453000002599</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.14226474000001799</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.164695030000029</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.18702865000000199</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.20919062999996599</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.229304070000034</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.24864232999998401</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.27238376999998698</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.294165449999991</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.31352213999998602</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-8F23-43BC-9E7A-09DB3455A3DB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>MS!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>FLAT</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>MS!$A$2:$A$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>60000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>70000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>80000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>90000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>110000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>120000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>130000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>140000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>150000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>MS!$E$2:$E$16</c:f>
+              <c:numCache>
+                <c:formatCode>0.00000</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>1.5653199999997001E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.1338310000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.1110870000002202E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.0834349999995494E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.4614740000006294E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.9418790000026999E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.117413970000006</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.134773660000018</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.154947579999998</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.170236430000022</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.18890194000000499</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.20853489000000899</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.22714252000000601</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.245429439999998</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.26384250000000897</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-8F23-43BC-9E7A-09DB3455A3DB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>MS!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>V SHAPE</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3392,263 +3780,116 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>MS!$I$3:$I$17</c:f>
+              <c:f>MS!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>20000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>30000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>40000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6</c:v>
+                  <c:v>60000</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7</c:v>
+                  <c:v>70000</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8</c:v>
+                  <c:v>80000</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9</c:v>
+                  <c:v>90000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>11</c:v>
+                  <c:v>110000</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>12</c:v>
+                  <c:v>120000</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>13</c:v>
+                  <c:v>130000</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>14</c:v>
+                  <c:v>140000</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>15</c:v>
+                  <c:v>150000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>MS!$H$3:$H$17</c:f>
+              <c:f>MS!$F$2:$F$16</c:f>
               <c:numCache>
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>1.6860090000000098E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.24042599999756E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.4209910000008597E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.4716889999990599E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.1542620000018296E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.106035139999994</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.12621419000001799</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.14530125999999599</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.16312177999998301</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.18419293000001699</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.210099190000028</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.240699289999975</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.25257817999999999</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.27556503999999199</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.29787633000000802</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-72E2-47EE-9E7F-E08A698202E6}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>MS!$K$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>FLAT</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>MS!$L$3:$L$17</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>MS!$K$3:$K$17</c:f>
-              <c:numCache>
-                <c:formatCode>0.00000</c:formatCode>
-                <c:ptCount val="15"/>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-72E2-47EE-9E7F-E08A698202E6}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>MS!$N$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>V SHAPE</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>MS!$O$3:$O$17</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>MS!$N$3:$N$17</c:f>
-              <c:numCache>
-                <c:formatCode>0.00000</c:formatCode>
-                <c:ptCount val="15"/>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-72E2-47EE-9E7F-E08A698202E6}"/>
+              <c16:uniqueId val="{00000004-8F23-43BC-9E7A-09DB3455A3DB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3660,14 +3901,16 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="723363720"/>
-        <c:axId val="723360120"/>
+        <c:axId val="837922360"/>
+        <c:axId val="837919840"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="723363720"/>
+        <c:axId val="837922360"/>
         <c:scaling>
           <c:logBase val="2"/>
           <c:orientation val="minMax"/>
+          <c:max val="160000"/>
+          <c:min val="10000"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -3685,7 +3928,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="#,##0\K" sourceLinked="0"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3722,12 +3965,12 @@
             <a:endParaRPr lang="pl-PL"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="723360120"/>
+        <c:crossAx val="837919840"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="723360120"/>
+        <c:axId val="837919840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3747,7 +3990,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+        <c:numFmt formatCode="0.00000" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3784,10 +4027,9 @@
             <a:endParaRPr lang="pl-PL"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="723363720"/>
+        <c:crossAx val="837922360"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
-        <c:majorUnit val="0.2"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -3906,10 +4148,13 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Q</a:t>
+            </a:r>
+            <a:r>
               <a:rPr lang="pl-PL"/>
-              <a:t>QS</a:t>
+              <a:t>S</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -3938,7 +4183,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="pl-PL"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -3953,7 +4198,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>QS!$B$1</c:f>
+              <c:f>QS!$B$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3965,7 +4210,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="00B0F0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -3975,71 +4220,81 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:xVal>
-            <c:strRef>
-              <c:f>QS!$B$3:$C$17</c:f>
-              <c:strCache>
-                <c:ptCount val="15"/>
+            <c:numRef>
+              <c:f>QS!$D$1:$L$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>200</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>400</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
+                  <c:v>500</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7</c:v>
+                  <c:v>700</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8</c:v>
+                  <c:v>800</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+                  <c:v>900</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>QS!$B$3:$B$17</c:f>
+              <c:f>QS!$D$2:$L$2</c:f>
               <c:numCache>
-                <c:formatCode>0.00000</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:formatCode>0.0000000</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>7.17330002225935E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.4334999953862204E-4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.5708000008016799E-4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0421999992104201E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.2964599998667801E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.4042499999049999E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.4908999990439001E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.55782999936491E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.6475899989018201E-3</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-368A-4447-9F1D-F10CFEFD7F11}"/>
+              <c16:uniqueId val="{00000000-D4E1-482F-8055-8B4646E50068}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4048,7 +4303,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>QS!$E$1</c:f>
+              <c:f>QS!$B$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4071,71 +4326,80 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>QS!$F$3:$F$17</c:f>
+              <c:f>QS!$D$1:$L$1</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>200</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>400</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
+                  <c:v>500</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7</c:v>
+                  <c:v>700</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8</c:v>
+                  <c:v>800</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>QS!$E$3:$E$17</c:f>
+              <c:f>QS!$D$3:$L$3</c:f>
               <c:numCache>
-                <c:formatCode>0.00000</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:formatCode>0.0000000</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>2.3945000139065001E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.1512999818660299E-4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.2178900011349399E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.9513399980496599E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.0918299977201898E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.4002500013448301E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6.1177800002042201E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.4757599999429603E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.1746099991723892E-3</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-368A-4447-9F1D-F10CFEFD7F11}"/>
+              <c16:uniqueId val="{00000001-D4E1-482F-8055-8B4646E50068}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4144,7 +4408,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>QS!$H$1</c:f>
+              <c:f>QS!$B$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4167,71 +4431,80 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>QS!$I$3:$I$17</c:f>
+              <c:f>QS!$D$1:$L$1</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>200</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>400</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
+                  <c:v>500</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7</c:v>
+                  <c:v>700</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8</c:v>
+                  <c:v>800</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>QS!$H$3:$H$17</c:f>
+              <c:f>QS!$D$4:$L$4</c:f>
               <c:numCache>
-                <c:formatCode>0.00000</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>4.4845999800600098E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0656999977072699E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.3012400022707799E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.0465000027324997E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.8049900020705498E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8.4697399986907798E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.1194689999683699E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.4471140000387E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.83346799982246E-2</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-368A-4447-9F1D-F10CFEFD7F11}"/>
+              <c16:uniqueId val="{00000002-D4E1-482F-8055-8B4646E50068}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4243,14 +4516,15 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="723363720"/>
-        <c:axId val="723360120"/>
+        <c:axId val="348094360"/>
+        <c:axId val="798688928"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="723363720"/>
+        <c:axId val="348094360"/>
         <c:scaling>
           <c:logBase val="2"/>
           <c:orientation val="minMax"/>
+          <c:min val="100"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -4268,7 +4542,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="#,##0\K" sourceLinked="0"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4305,12 +4579,12 @@
             <a:endParaRPr lang="pl-PL"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="723360120"/>
+        <c:crossAx val="798688928"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="723360120"/>
+        <c:axId val="798688928"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4330,7 +4604,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+        <c:numFmt formatCode="0.0000000" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4367,10 +4641,9 @@
             <a:endParaRPr lang="pl-PL"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="723363720"/>
+        <c:crossAx val="348094360"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
-        <c:majorUnit val="0.2"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -7239,29 +7512,27 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>485775</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>4761</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>66674</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Wykres 2">
+        <xdr:cNvPr id="2" name="Wykres 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60C278BC-C065-43CE-B9CC-6379710BB636}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{991C4CB2-8860-EE72-D420-039D0E4E67F0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -7282,29 +7553,27 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>133349</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>390525</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>33337</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Wykres 1">
+        <xdr:cNvPr id="3" name="Wykres 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFA41BDF-A59D-4C0C-98C7-513ECD5F1740}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F396E6A-3122-5D13-870B-0922F6760D58}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -7325,29 +7594,27 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>114299</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>14287</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>19051</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Wykres 1">
+        <xdr:cNvPr id="3" name="Wykres 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BD42BC3-5CC3-4CA4-972D-A41EE6E32955}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55B5F4D4-099D-A403-17D6-A53B0803FE89}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -7368,29 +7635,27 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>295275</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Wykres 1">
+        <xdr:cNvPr id="3" name="Wykres 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E45DBC82-67B1-4C67-8DB4-AC6D1A5C3EE9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93A656E0-EC3D-FB9C-08D8-D7BB32B63EFA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -7411,29 +7676,27 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>552449</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>14286</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>152399</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Wykres 1">
+        <xdr:cNvPr id="3" name="Wykres 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CA9C264-7692-45F0-94AF-91DB5B32A92C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F7D3A15-FC26-2672-6E19-EBD0510692C3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -7747,569 +8010,431 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B30C56E8-06B5-4DC8-9A83-1482F52FEB5E}">
-  <dimension ref="B1:O17"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
       <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" t="s">
         <v>5</v>
       </c>
-      <c r="N1" t="s">
+      <c r="F1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>2</v>
-      </c>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>5000</v>
+      </c>
+      <c r="B2">
+        <v>0.30721069999981399</v>
+      </c>
+      <c r="C2">
+        <v>1.54730000031122E-3</v>
+      </c>
+      <c r="D2">
+        <v>0.57234600000037905</v>
+      </c>
+      <c r="E2" s="6">
+        <v>3.9689999994152399E-4</v>
+      </c>
+      <c r="F2">
+        <v>0.28953629999978098</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>6000</v>
+      </c>
       <c r="B3" s="2">
-        <v>1.2026800000001E-2</v>
+        <v>0.45558799999980598</v>
       </c>
       <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2">
-        <v>3.2405000001745001E-4</v>
+        <v>1.8291000001227E-3</v>
+      </c>
+      <c r="D3">
+        <v>0.87804570000025695</v>
+      </c>
+      <c r="E3" s="7">
+        <v>4.6110000039334398E-4</v>
       </c>
       <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="H3" s="3">
-        <v>2.37475000003541E-2</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1</v>
-      </c>
-      <c r="K3" s="3">
-        <v>3.3773999994082202E-4</v>
-      </c>
-      <c r="L3" s="1">
-        <v>4</v>
-      </c>
+        <v>0.43907510000008099</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="1"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="1"/>
       <c r="N3" s="3"/>
-      <c r="O3" s="1">
-        <v>1</v>
-      </c>
+      <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>7000</v>
+      </c>
       <c r="B4" s="2">
-        <v>4.7352119999999297E-2</v>
+        <v>0.60786150000012595</v>
       </c>
       <c r="C4">
-        <f>C3+1</f>
-        <v>2</v>
-      </c>
-      <c r="E4" s="2">
-        <v>7.0988000002216703E-4</v>
+        <v>2.23740000001271E-3</v>
+      </c>
+      <c r="D4">
+        <v>1.13276829999995</v>
+      </c>
+      <c r="E4" s="7">
+        <v>5.3290000005290397E-4</v>
       </c>
       <c r="F4">
-        <f>F3+1</f>
-        <v>2</v>
-      </c>
-      <c r="H4" s="3">
-        <v>9.3164099999739805E-2</v>
-      </c>
-      <c r="I4" s="1">
-        <f>I3+1</f>
-        <v>2</v>
-      </c>
-      <c r="K4" s="3">
-        <v>4.1441000003032902E-4</v>
-      </c>
-      <c r="L4" s="1">
-        <f>L3+1</f>
-        <v>5</v>
-      </c>
+        <v>0.60516770000003794</v>
+      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" s="1"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="1"/>
       <c r="N4" s="3"/>
-      <c r="O4" s="1">
-        <f>O3+1</f>
-        <v>2</v>
-      </c>
+      <c r="O4" s="1"/>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>8000</v>
+      </c>
       <c r="B5" s="2">
-        <v>0.101906809999996</v>
+        <v>0.77074999999967897</v>
       </c>
       <c r="C5">
-        <f t="shared" ref="C5:C17" si="0">C4+1</f>
-        <v>3</v>
-      </c>
-      <c r="E5" s="2">
-        <v>1.0198499999660199E-3</v>
+        <v>2.72189999986949E-3</v>
+      </c>
+      <c r="D5">
+        <v>1.42819370000006</v>
+      </c>
+      <c r="E5" s="7">
+        <v>6.5750000021580404E-4</v>
       </c>
       <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="H5" s="3">
-        <v>0.21513779999986499</v>
-      </c>
-      <c r="I5" s="1">
-        <f t="shared" ref="I5:I17" si="1">I4+1</f>
-        <v>3</v>
-      </c>
-      <c r="K5" s="3">
-        <v>4.8261000001730199E-4</v>
-      </c>
-      <c r="L5" s="1">
-        <f t="shared" ref="L5:L17" si="2">L4+1</f>
-        <v>6</v>
-      </c>
+        <v>0.76325990000032096</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="1"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="1"/>
       <c r="N5" s="3"/>
-      <c r="O5" s="1">
-        <f t="shared" ref="O5:O17" si="3">O4+1</f>
-        <v>3</v>
-      </c>
+      <c r="O5" s="1"/>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>9000</v>
+      </c>
       <c r="B6" s="2">
-        <v>0.172704049999998</v>
+        <v>0.961230200000045</v>
       </c>
       <c r="C6">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="E6" s="2">
-        <v>1.36506999997436E-3</v>
+        <v>3.0435000003308202E-3</v>
+      </c>
+      <c r="D6">
+        <v>1.8054827000000799</v>
+      </c>
+      <c r="E6" s="7">
+        <v>7.1089999983087095E-4</v>
       </c>
       <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="H6" s="3">
-        <v>0.383297599999878</v>
-      </c>
-      <c r="I6" s="1">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="K6" s="3">
-        <v>6.0788000000684401E-4</v>
-      </c>
-      <c r="L6" s="1">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
+        <v>0.96820669999988196</v>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="1"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="1"/>
       <c r="N6" s="3"/>
-      <c r="O6" s="1">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
+      <c r="O6" s="1"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>10000</v>
+      </c>
       <c r="B7" s="2">
-        <v>0.265004980000003</v>
+        <v>1.1705431000000299</v>
       </c>
       <c r="C7">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="E7" s="2">
-        <v>1.6877099999874101E-3</v>
+        <v>3.38460000011764E-3</v>
+      </c>
+      <c r="D7">
+        <v>2.2503299999998401</v>
+      </c>
+      <c r="E7" s="7">
+        <v>7.6600000011239899E-4</v>
       </c>
       <c r="F7">
-        <v>5</v>
-      </c>
-      <c r="H7" s="3">
-        <v>0.59812620000002403</v>
-      </c>
-      <c r="I7" s="1">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="K7" s="3">
-        <v>6.5556999998079798E-4</v>
-      </c>
-      <c r="L7" s="1">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
+        <v>1.15225519999967</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="1"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="1"/>
       <c r="N7" s="3"/>
-      <c r="O7" s="1">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
+      <c r="O7" s="1"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>11000</v>
+      </c>
       <c r="B8" s="2">
-        <v>0.38173197000000397</v>
+        <v>1.4176434000000799</v>
       </c>
       <c r="C8">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="E8" s="2">
-        <v>1.9887099999778002E-3</v>
+        <v>3.60510000018621E-3</v>
+      </c>
+      <c r="D8">
+        <v>2.7179971000000398</v>
+      </c>
+      <c r="E8" s="7">
+        <v>8.4030000016355102E-4</v>
       </c>
       <c r="F8">
-        <v>6</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0.85802510000030396</v>
-      </c>
-      <c r="I8" s="1">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="K8" s="3">
-        <v>7.1244000000660805E-4</v>
-      </c>
-      <c r="L8" s="1">
-        <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
+        <v>1.4153353000001501</v>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="I8" s="1"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="1"/>
       <c r="N8" s="3"/>
-      <c r="O8" s="1">
-        <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
+      <c r="O8" s="1"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>12000</v>
+      </c>
       <c r="B9" s="2">
-        <v>0.51714583999999997</v>
+        <v>1.76679779999994</v>
       </c>
       <c r="C9">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="E9" s="2">
-        <v>2.3997400000098398E-3</v>
+        <v>3.8497000000461399E-3</v>
+      </c>
+      <c r="D9">
+        <v>3.1981657000001098</v>
+      </c>
+      <c r="E9" s="7">
+        <v>9.7079999977722699E-4</v>
       </c>
       <c r="F9">
-        <v>7</v>
-      </c>
-      <c r="H9" s="3">
-        <v>1.1713122000000999</v>
-      </c>
-      <c r="I9" s="1">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="K9" s="3">
-        <v>8.1143999996129395E-4</v>
-      </c>
-      <c r="L9" s="1">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
+        <v>1.7971864999999501</v>
+      </c>
+      <c r="H9" s="3"/>
+      <c r="I9" s="1"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="1"/>
       <c r="N9" s="3"/>
-      <c r="O9" s="1">
-        <f t="shared" si="3"/>
-        <v>7</v>
-      </c>
+      <c r="O9" s="1"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>13000</v>
+      </c>
       <c r="B10" s="2">
-        <v>0.67668937000000196</v>
+        <v>1.9851642999997201</v>
       </c>
       <c r="C10">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="E10" s="2">
-        <v>2.68952000001263E-3</v>
+        <v>4.3052999999417798E-3</v>
+      </c>
+      <c r="D10">
+        <v>3.7459339000001801</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1.17610000006607E-3</v>
       </c>
       <c r="F10">
-        <v>8</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1.5260954999998799</v>
-      </c>
-      <c r="I10" s="1">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="K10" s="3">
-        <v>8.7516999992658302E-4</v>
-      </c>
-      <c r="L10" s="1">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
+        <v>1.9297953000000201</v>
+      </c>
+      <c r="H10" s="3"/>
+      <c r="I10" s="1"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="1"/>
       <c r="N10" s="3"/>
-      <c r="O10" s="1">
-        <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
+      <c r="O10" s="1"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>14000</v>
+      </c>
       <c r="B11" s="2">
-        <v>0.85694406999999695</v>
+        <v>2.3113642999996902</v>
       </c>
       <c r="C11">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="E11" s="2">
-        <v>2.9708799999752901E-3</v>
+        <v>4.6677999998791997E-3</v>
+      </c>
+      <c r="D11">
+        <v>4.4209681000002004</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.0643999999047E-3</v>
       </c>
       <c r="F11">
-        <v>9</v>
-      </c>
-      <c r="H11" s="3">
-        <v>1.9465801999999699</v>
-      </c>
-      <c r="I11" s="1">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="K11" s="3">
-        <v>9.4318000001294402E-4</v>
-      </c>
-      <c r="L11" s="1">
-        <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
+        <v>2.2352631999997299</v>
+      </c>
+      <c r="H11" s="3"/>
+      <c r="I11" s="1"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="1"/>
       <c r="N11" s="3"/>
-      <c r="O11" s="1">
-        <f t="shared" si="3"/>
-        <v>9</v>
-      </c>
+      <c r="O11" s="1"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>15000</v>
+      </c>
       <c r="B12" s="2">
-        <v>1.0538272799999999</v>
+        <v>2.6444400999998798</v>
       </c>
       <c r="C12">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="E12" s="2">
-        <v>3.3418200000141902E-3</v>
+        <v>4.8817000001690697E-3</v>
+      </c>
+      <c r="D12">
+        <v>5.0299622999996201</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.2022999999317099E-3</v>
       </c>
       <c r="F12">
-        <v>10</v>
-      </c>
-      <c r="H12" s="3">
-        <v>2.3870911999997499</v>
-      </c>
-      <c r="I12" s="1">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="K12" s="3">
-        <v>9.8740999992514796E-4</v>
-      </c>
-      <c r="L12" s="1">
-        <f t="shared" si="2"/>
-        <v>13</v>
-      </c>
+        <v>2.6419641000002199</v>
+      </c>
+      <c r="H12" s="3"/>
+      <c r="I12" s="1"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="1"/>
       <c r="N12" s="3"/>
-      <c r="O12" s="1">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
+      <c r="O12" s="1"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>16000</v>
+      </c>
       <c r="B13" s="2">
-        <v>1.29810537</v>
+        <v>3.0175906999998001</v>
       </c>
       <c r="C13">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="E13" s="2">
-        <v>3.70965000001888E-3</v>
+        <v>5.7689999998729001E-3</v>
+      </c>
+      <c r="D13">
+        <v>5.7007025000002596</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.2292999999772201E-3</v>
       </c>
       <c r="F13">
-        <v>11</v>
-      </c>
-      <c r="H13" s="3">
-        <v>2.82016909999993</v>
-      </c>
-      <c r="I13" s="1">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="K13" s="3">
-        <v>1.08957000002192E-3</v>
-      </c>
-      <c r="L13" s="1">
-        <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
+        <v>3.1611447000000199</v>
+      </c>
+      <c r="H13" s="3"/>
+      <c r="I13" s="1"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="1"/>
       <c r="N13" s="3"/>
-      <c r="O13" s="1">
-        <f t="shared" si="3"/>
-        <v>11</v>
-      </c>
+      <c r="O13" s="1"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>17000</v>
+      </c>
       <c r="B14" s="2">
-        <v>1.5276361599999999</v>
+        <v>3.3604879999997999</v>
       </c>
       <c r="C14">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="E14" s="2">
-        <v>4.0137399999821298E-3</v>
+        <v>5.7770999997046601E-3</v>
+      </c>
+      <c r="D14">
+        <v>6.49658449999969</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1.3216000002103101E-3</v>
       </c>
       <c r="F14">
-        <v>12</v>
-      </c>
-      <c r="H14" s="3">
-        <v>3.3512731999999201</v>
-      </c>
-      <c r="I14" s="1">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="K14" s="3">
-        <v>1.2249800000063199E-3</v>
-      </c>
-      <c r="L14" s="1">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
+        <v>3.58185110000022</v>
+      </c>
+      <c r="H14" s="3"/>
+      <c r="I14" s="1"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="1"/>
       <c r="N14" s="3"/>
-      <c r="O14" s="1">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
+      <c r="O14" s="1"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>18000</v>
+      </c>
       <c r="B15" s="2">
-        <v>1.7970345999999999</v>
+        <v>3.8151886999998998</v>
       </c>
       <c r="C15">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="E15" s="2">
-        <v>4.4661199999609302E-3</v>
+        <v>6.0286999996606002E-3</v>
+      </c>
+      <c r="D15">
+        <v>7.2027017999998799</v>
+      </c>
+      <c r="E15" s="7">
+        <v>1.3784000002488E-3</v>
       </c>
       <c r="F15">
-        <v>13</v>
-      </c>
-      <c r="H15" s="3">
-        <v>3.89625109999997</v>
-      </c>
-      <c r="I15" s="1">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="K15" s="3">
-        <v>1.2250200000380499E-3</v>
-      </c>
-      <c r="L15" s="1">
-        <f t="shared" si="2"/>
-        <v>16</v>
-      </c>
+        <v>3.97890750000033</v>
+      </c>
+      <c r="H15" s="3"/>
+      <c r="I15" s="1"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="1"/>
       <c r="N15" s="3"/>
-      <c r="O15" s="1">
-        <f t="shared" si="3"/>
-        <v>13</v>
-      </c>
+      <c r="O15" s="1"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>19000</v>
+      </c>
       <c r="B16" s="2">
-        <v>2.0782094199999999</v>
+        <v>4.2824634999997198</v>
       </c>
       <c r="C16">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="E16" s="2">
-        <v>4.6943299999838897E-3</v>
+        <v>6.2232999998741399E-3</v>
+      </c>
+      <c r="D16">
+        <v>8.0657694000001303</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1.6263000002254501E-3</v>
       </c>
       <c r="F16">
-        <v>14</v>
-      </c>
-      <c r="H16" s="3">
-        <v>4.5177859999998802</v>
-      </c>
-      <c r="I16" s="1">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="K16" s="3">
-        <v>1.47315000000162E-2</v>
-      </c>
-      <c r="L16" s="1">
-        <f t="shared" si="2"/>
-        <v>17</v>
-      </c>
+        <v>4.4468391000000302</v>
+      </c>
+      <c r="H16" s="3"/>
+      <c r="I16" s="1"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="1"/>
       <c r="N16" s="3"/>
-      <c r="O16" s="1">
-        <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
+      <c r="O16" s="1"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B17" s="2">
-        <v>2.3782967500000001</v>
-      </c>
-      <c r="C17">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="E17" s="2">
-        <v>5.3557199999886501E-3</v>
-      </c>
-      <c r="F17">
-        <f>F16+1</f>
-        <v>15</v>
-      </c>
-      <c r="H17" s="3">
-        <v>5.2451040000000804</v>
-      </c>
-      <c r="I17" s="1">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="K17" s="3">
-        <v>1.5473400000701001E-3</v>
-      </c>
-      <c r="L17" s="1">
-        <f t="shared" si="2"/>
-        <v>18</v>
-      </c>
+      <c r="B17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="1"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="1"/>
       <c r="N17" s="3"/>
-      <c r="O17" s="1">
-        <f t="shared" si="3"/>
-        <v>15</v>
-      </c>
+      <c r="O17" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8319,509 +8444,439 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{371580CD-EA1C-4357-8346-4806FE3F1D81}">
-  <dimension ref="B1:O17"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
     </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>2</v>
-      </c>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>5000</v>
+      </c>
+      <c r="B2" s="3">
+        <v>0.29711640000004902</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0.27801170000020597</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.371550500000012</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0.26314849999971501</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0.29711640000004902</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>6000</v>
+      </c>
       <c r="B3" s="3">
-        <v>1.13804100000038E-2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3">
-        <v>1</v>
+        <v>0.42092019999972702</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0.39111229999980401</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0.404069400000025</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0.37396750000016199</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0.42092019999972702</v>
       </c>
       <c r="H3" s="3"/>
-      <c r="I3" s="1">
-        <v>1</v>
-      </c>
-      <c r="K3" s="3">
-        <v>1.1810930000001401E-2</v>
-      </c>
-      <c r="L3" s="1">
-        <v>1</v>
-      </c>
+      <c r="I3" s="1"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="1"/>
       <c r="N3" s="3"/>
-      <c r="O3" s="1">
-        <v>1</v>
-      </c>
+      <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>7000</v>
+      </c>
       <c r="B4" s="3">
-        <v>4.4423310000001902E-2</v>
-      </c>
-      <c r="C4">
-        <f>C3+1</f>
-        <v>2</v>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4">
-        <f>F3+1</f>
-        <v>2</v>
+        <v>0.56643490000033103</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.561001900000064</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0.56454829999984202</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0.529808199999934</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.56643490000033103</v>
       </c>
       <c r="H4" s="3"/>
-      <c r="I4" s="1">
-        <f>I3+1</f>
-        <v>2</v>
-      </c>
-      <c r="K4" s="3">
-        <v>4.5579520000001102E-2</v>
-      </c>
-      <c r="L4" s="1">
-        <f>L3+1</f>
-        <v>2</v>
-      </c>
+      <c r="I4" s="1"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="1"/>
       <c r="N4" s="3"/>
-      <c r="O4" s="1">
-        <f>O3+1</f>
-        <v>2</v>
-      </c>
+      <c r="O4" s="1"/>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>8000</v>
+      </c>
       <c r="B5" s="3">
-        <v>9.6786580000002606E-2</v>
-      </c>
-      <c r="C5">
-        <f t="shared" ref="C5:C17" si="0">C4+1</f>
-        <v>3</v>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5">
-        <v>3</v>
+        <v>0.689637999999831</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.92349749999993902</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0.73407259999976304</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0.71018950000006897</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.689637999999831</v>
       </c>
       <c r="H5" s="3"/>
-      <c r="I5" s="1">
-        <f t="shared" ref="I5:I17" si="1">I4+1</f>
-        <v>3</v>
-      </c>
-      <c r="K5" s="3">
-        <v>0.102432369999996</v>
-      </c>
-      <c r="L5" s="1">
-        <f t="shared" ref="L5:L17" si="2">L4+1</f>
-        <v>3</v>
-      </c>
+      <c r="I5" s="1"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="1"/>
       <c r="N5" s="3"/>
-      <c r="O5" s="1">
-        <f t="shared" ref="O5:O17" si="3">O4+1</f>
-        <v>3</v>
-      </c>
+      <c r="O5" s="1"/>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>9000</v>
+      </c>
       <c r="B6" s="3">
-        <v>0.161760220000007</v>
-      </c>
-      <c r="C6">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6">
-        <v>4</v>
+        <v>0.93152640000016596</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0.86902899999995498</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0.92283070000030398</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.84070620000011298</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.93152640000016596</v>
       </c>
       <c r="H6" s="3"/>
-      <c r="I6" s="1">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="K6" s="3">
-        <v>0.17761743000000901</v>
-      </c>
-      <c r="L6" s="1">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
+      <c r="I6" s="1"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="1"/>
       <c r="N6" s="3"/>
-      <c r="O6" s="1">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
+      <c r="O6" s="1"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>10000</v>
+      </c>
       <c r="B7" s="3">
-        <v>0.25599808999999102</v>
-      </c>
-      <c r="C7">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7">
-        <v>5</v>
+        <v>1.1448983999998701</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1.10183499999993</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1.1276714999999</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1.0199678999997499</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1.1448983999998701</v>
       </c>
       <c r="H7" s="3"/>
-      <c r="I7" s="1">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="K7" s="3">
-        <v>0.27528482000000098</v>
-      </c>
-      <c r="L7" s="1">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
+      <c r="I7" s="1"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="1"/>
       <c r="N7" s="3"/>
-      <c r="O7" s="1">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
+      <c r="O7" s="1"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>11000</v>
+      </c>
       <c r="B8" s="3">
-        <v>0.35797905999999102</v>
-      </c>
-      <c r="C8">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8">
-        <v>6</v>
+        <v>1.2892377000002799</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1.3148572000000001</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1.77930940000032</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1.24446809999972</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1.2892377000002799</v>
       </c>
       <c r="H8" s="3"/>
-      <c r="I8" s="1">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="K8" s="3">
-        <v>0.39591920000000302</v>
-      </c>
-      <c r="L8" s="1">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
+      <c r="I8" s="1"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="1"/>
       <c r="N8" s="3"/>
-      <c r="O8" s="1">
-        <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
+      <c r="O8" s="1"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>12000</v>
+      </c>
       <c r="B9" s="3">
-        <v>0.49104384999999401</v>
-      </c>
-      <c r="C9">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="E9" s="2"/>
-      <c r="F9">
-        <v>7</v>
+        <v>1.6510609000001699</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1.5503923000001101</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1.6312573999998601</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1.49062700000013</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1.6510609000001699</v>
       </c>
       <c r="H9" s="3"/>
-      <c r="I9" s="1">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="K9" s="3">
-        <v>0.52693365999998598</v>
-      </c>
-      <c r="L9" s="1">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
+      <c r="I9" s="1"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="1"/>
       <c r="N9" s="3"/>
-      <c r="O9" s="1">
-        <f t="shared" si="3"/>
-        <v>7</v>
-      </c>
+      <c r="O9" s="1"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>13000</v>
+      </c>
       <c r="B10" s="3">
-        <v>0.638195540000003</v>
-      </c>
-      <c r="C10">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10">
-        <v>8</v>
+        <v>1.7719887000002901</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1.8155158999998</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1.89283960000011</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1.77890509999997</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1.7719887000002901</v>
       </c>
       <c r="H10" s="3"/>
-      <c r="I10" s="1">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="K10" s="3">
-        <v>0.69100402000001304</v>
-      </c>
-      <c r="L10" s="1">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
+      <c r="I10" s="1"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="1"/>
       <c r="N10" s="3"/>
-      <c r="O10" s="1">
-        <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
+      <c r="O10" s="1"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>14000</v>
+      </c>
       <c r="B11" s="3">
-        <v>0.81029029999999602</v>
-      </c>
-      <c r="C11">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11">
-        <v>9</v>
+        <v>2.23256409999976</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2.7273538999997902</v>
+      </c>
+      <c r="D11" s="2">
+        <v>2.1945440000004002</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2.02817709999999</v>
+      </c>
+      <c r="F11" s="2">
+        <v>2.23256409999976</v>
       </c>
       <c r="H11" s="3"/>
-      <c r="I11" s="1">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="K11" s="3">
-        <v>0.90792875999998102</v>
-      </c>
-      <c r="L11" s="1">
-        <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
+      <c r="I11" s="1"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="1"/>
       <c r="N11" s="3"/>
-      <c r="O11" s="1">
-        <f t="shared" si="3"/>
-        <v>9</v>
-      </c>
+      <c r="O11" s="1"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>15000</v>
+      </c>
       <c r="B12" s="3">
-        <v>1.00392338</v>
-      </c>
-      <c r="C12">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12">
-        <v>10</v>
+        <v>2.5738467999999499</v>
+      </c>
+      <c r="C12" s="2">
+        <v>2.35320389999969</v>
+      </c>
+      <c r="D12" s="2">
+        <v>2.50375829999984</v>
+      </c>
+      <c r="E12" s="2">
+        <v>2.3299543999996701</v>
+      </c>
+      <c r="F12" s="2">
+        <v>2.5738467999999499</v>
       </c>
       <c r="H12" s="3"/>
-      <c r="I12" s="1">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="K12" s="3">
-        <v>1.1209079099999799</v>
-      </c>
-      <c r="L12" s="1">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
+      <c r="I12" s="1"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="1"/>
       <c r="N12" s="3"/>
-      <c r="O12" s="1">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
+      <c r="O12" s="1"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>16000</v>
+      </c>
       <c r="B13" s="3">
-        <v>1.2179960299999899</v>
-      </c>
-      <c r="C13">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13">
-        <v>11</v>
+        <v>2.7353607000000002</v>
+      </c>
+      <c r="C13" s="2">
+        <v>2.7455755999999298</v>
+      </c>
+      <c r="D13" s="2">
+        <v>2.8445698000000399</v>
+      </c>
+      <c r="E13" s="2">
+        <v>2.6098971999999701</v>
+      </c>
+      <c r="F13" s="2">
+        <v>2.7353607000000002</v>
       </c>
       <c r="H13" s="3"/>
-      <c r="I13" s="1">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="K13" s="3">
-        <v>1.35179544999998</v>
-      </c>
-      <c r="L13" s="1">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
+      <c r="I13" s="1"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="1"/>
       <c r="N13" s="3"/>
-      <c r="O13" s="1">
-        <f t="shared" si="3"/>
-        <v>11</v>
-      </c>
+      <c r="O13" s="1"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>17000</v>
+      </c>
       <c r="B14" s="3">
-        <v>1.45096204999999</v>
-      </c>
-      <c r="C14">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14">
-        <v>12</v>
+        <v>3.3449150000001202</v>
+      </c>
+      <c r="C14" s="2">
+        <v>3.0529510999999698</v>
+      </c>
+      <c r="D14" s="2">
+        <v>4.2412036000000599</v>
+      </c>
+      <c r="E14" s="2">
+        <v>2.99417149999999</v>
+      </c>
+      <c r="F14" s="2">
+        <v>3.3449150000001202</v>
       </c>
       <c r="H14" s="3"/>
-      <c r="I14" s="1">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="K14" s="3">
-        <v>1.6097550999999799</v>
-      </c>
-      <c r="L14" s="1">
-        <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
+      <c r="I14" s="1"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="1"/>
       <c r="N14" s="3"/>
-      <c r="O14" s="1">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
+      <c r="O14" s="1"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>18000</v>
+      </c>
       <c r="B15" s="3">
-        <v>1.70663114</v>
-      </c>
-      <c r="C15">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15">
-        <v>13</v>
+        <v>3.40162020000025</v>
+      </c>
+      <c r="C15" s="2">
+        <v>3.44943740000007</v>
+      </c>
+      <c r="D15" s="2">
+        <v>3.6253870999998901</v>
+      </c>
+      <c r="E15" s="2">
+        <v>3.33117489999995</v>
+      </c>
+      <c r="F15" s="2">
+        <v>3.40162020000025</v>
       </c>
       <c r="H15" s="3"/>
-      <c r="I15" s="1">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="K15" s="3">
-        <v>1.88213537999999</v>
-      </c>
-      <c r="L15" s="1">
-        <f t="shared" si="2"/>
-        <v>13</v>
-      </c>
+      <c r="I15" s="1"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="1"/>
       <c r="N15" s="3"/>
-      <c r="O15" s="1">
-        <f t="shared" si="3"/>
-        <v>13</v>
-      </c>
+      <c r="O15" s="1"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>19000</v>
+      </c>
       <c r="B16" s="3">
-        <v>1.99173796</v>
-      </c>
-      <c r="C16">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16">
-        <v>14</v>
+        <v>4.11404940000011</v>
+      </c>
+      <c r="C16" s="2">
+        <v>3.81637829999999</v>
+      </c>
+      <c r="D16" s="2">
+        <v>4.1029728000003098</v>
+      </c>
+      <c r="E16" s="2">
+        <v>3.7084792000000499</v>
+      </c>
+      <c r="F16" s="2">
+        <v>4.11404940000011</v>
       </c>
       <c r="H16" s="3"/>
-      <c r="I16" s="1">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="K16" s="3">
-        <v>2.1775392799999902</v>
-      </c>
-      <c r="L16" s="1">
-        <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
+      <c r="I16" s="1"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="1"/>
       <c r="N16" s="3"/>
-      <c r="O16" s="1">
-        <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
+      <c r="O16" s="1"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B17" s="3">
-        <v>2.4300448299999902</v>
-      </c>
-      <c r="C17">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
+      <c r="B17" s="3"/>
       <c r="E17" s="2"/>
-      <c r="F17">
-        <f>F16+1</f>
-        <v>15</v>
-      </c>
       <c r="H17" s="3"/>
-      <c r="I17" s="1">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="K17" s="3">
-        <v>2.4898922799999998</v>
-      </c>
-      <c r="L17" s="1">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
+      <c r="I17" s="1"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="1"/>
       <c r="N17" s="3"/>
-      <c r="O17" s="1">
-        <f t="shared" si="3"/>
-        <v>15</v>
-      </c>
+      <c r="O17" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8831,599 +8886,395 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D809587C-7A25-4025-BF6B-73480873253F}">
-  <dimension ref="B1:O17"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>2</v>
-      </c>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>10000</v>
+      </c>
+      <c r="B2" s="3">
+        <v>2.10359299999936E-2</v>
+      </c>
+      <c r="C2" s="2">
+        <v>2.27945099999942E-2</v>
+      </c>
+      <c r="D2" s="3">
+        <v>2.0781000000033599E-2</v>
+      </c>
+      <c r="E2" s="3">
+        <v>2.4259499999971E-3</v>
+      </c>
+      <c r="F2" s="3">
+        <v>1.9964449999997601E-2</v>
+      </c>
+      <c r="I2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="O2" s="1"/>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <f>A2+10^4</f>
+        <v>20000</v>
+      </c>
       <c r="B3" s="3">
-        <v>2.10359299999936E-2</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
-      </c>
-      <c r="E3" s="2">
-        <v>2.27945099999942E-2</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="H3" s="3">
-        <v>2.0781000000033599E-2</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1</v>
-      </c>
-      <c r="K3" s="3">
-        <v>2.4259499999971E-3</v>
-      </c>
-      <c r="L3" s="1">
-        <v>1</v>
-      </c>
-      <c r="N3" s="3">
-        <v>1.9964449999997601E-2</v>
-      </c>
-      <c r="O3" s="1">
-        <v>1</v>
-      </c>
+        <v>4.1789509999989601E-2</v>
+      </c>
+      <c r="C3" s="2">
+        <v>4.7945899999967803E-2</v>
+      </c>
+      <c r="D3" s="3">
+        <v>4.7866199999998499E-2</v>
+      </c>
+      <c r="E3" s="3">
+        <v>4.34314999999969E-3</v>
+      </c>
+      <c r="F3" s="3">
+        <v>4.3409370000017503E-2</v>
+      </c>
+      <c r="I3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <f t="shared" ref="A4:A16" si="0">A3+10^4</f>
+        <v>30000</v>
+      </c>
       <c r="B4" s="3">
-        <v>4.1789509999989601E-2</v>
-      </c>
-      <c r="C4">
-        <f>C3+10^1</f>
-        <v>20</v>
-      </c>
-      <c r="E4" s="2">
-        <v>4.7945899999967803E-2</v>
-      </c>
-      <c r="F4">
-        <f>F3+1</f>
-        <v>2</v>
-      </c>
-      <c r="H4" s="3">
-        <v>4.7866199999998499E-2</v>
-      </c>
-      <c r="I4" s="1">
-        <f>I3+1</f>
-        <v>2</v>
-      </c>
-      <c r="K4" s="3">
-        <v>4.34314999999969E-3</v>
-      </c>
-      <c r="L4" s="1">
-        <f>L3+1</f>
-        <v>2</v>
-      </c>
-      <c r="N4" s="3">
-        <v>4.3409370000017503E-2</v>
-      </c>
-      <c r="O4" s="1">
-        <f>O3+1</f>
-        <v>2</v>
-      </c>
+        <v>6.5792329999999302E-2</v>
+      </c>
+      <c r="C4" s="2">
+        <v>7.5582029999986797E-2</v>
+      </c>
+      <c r="D4" s="3">
+        <v>7.1616999999969205E-2</v>
+      </c>
+      <c r="E4" s="3">
+        <v>6.48232000000916E-3</v>
+      </c>
+      <c r="F4" s="3">
+        <v>6.7492769999989793E-2</v>
+      </c>
+      <c r="I4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="O4" s="1"/>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <f t="shared" si="0"/>
+        <v>40000</v>
+      </c>
       <c r="B5" s="3">
-        <v>6.5792329999999302E-2</v>
-      </c>
-      <c r="C5">
-        <f t="shared" ref="C5:C17" si="0">C4+10^1</f>
-        <v>30</v>
-      </c>
-      <c r="E5" s="2">
-        <v>7.5582029999986797E-2</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="H5" s="3">
-        <v>7.1616999999969205E-2</v>
-      </c>
-      <c r="I5" s="1">
-        <f t="shared" ref="I5:I17" si="1">I4+1</f>
-        <v>3</v>
-      </c>
-      <c r="K5" s="3">
-        <v>6.48232000000916E-3</v>
-      </c>
-      <c r="L5" s="1">
-        <f t="shared" ref="L5:L17" si="2">L4+1</f>
-        <v>3</v>
-      </c>
-      <c r="N5" s="3">
-        <v>6.7492769999989793E-2</v>
-      </c>
-      <c r="O5" s="1">
-        <f t="shared" ref="O5:O17" si="3">O4+1</f>
-        <v>3</v>
-      </c>
+        <v>8.81689399999913E-2</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.102748380000002</v>
+      </c>
+      <c r="D5" s="3">
+        <v>9.8706680000031993E-2</v>
+      </c>
+      <c r="E5" s="3">
+        <v>8.7847700000111203E-3</v>
+      </c>
+      <c r="F5" s="3">
+        <v>9.1893489999983993E-2</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="O5" s="1"/>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <f t="shared" si="0"/>
+        <v>50000</v>
+      </c>
       <c r="B6" s="3">
-        <v>8.81689399999913E-2</v>
-      </c>
-      <c r="C6">
+        <v>0.110551459999987</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0.12973804999996899</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.12213872999996001</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1.1156970000001799E-2</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0.116522420000001</v>
+      </c>
+      <c r="I6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="O6" s="1"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7">
         <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0.102748380000002</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="H6" s="3">
-        <v>9.8706680000031993E-2</v>
-      </c>
-      <c r="I6" s="1">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="K6" s="3">
-        <v>8.7847700000111203E-3</v>
-      </c>
-      <c r="L6" s="1">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="N6" s="3">
-        <v>9.1893489999983993E-2</v>
-      </c>
-      <c r="O6" s="1">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
+        <v>60000</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0.13445716000001001</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.15872756000003299</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.14884196999996599</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1.3060779999977901E-2</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.144577089999984</v>
+      </c>
+      <c r="I7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="O7" s="1"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B7" s="3">
-        <v>0.110551459999987</v>
-      </c>
-      <c r="C7">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8">
         <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0.12973804999996899</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-      <c r="H7" s="3">
-        <v>0.12213872999996001</v>
-      </c>
-      <c r="I7" s="1">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="K7" s="3">
-        <v>1.1156970000001799E-2</v>
-      </c>
-      <c r="L7" s="1">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="N7" s="3">
-        <v>0.116522420000001</v>
-      </c>
-      <c r="O7" s="1">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
+        <v>70000</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0.161532459999989</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.185764670000025</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.17582784000001001</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1.5788879999990901E-2</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.170943110000007</v>
+      </c>
+      <c r="I8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="O8" s="1"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B8" s="3">
-        <v>0.13445716000001001</v>
-      </c>
-      <c r="C8">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9">
         <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0.15872756000003299</v>
-      </c>
-      <c r="F8">
-        <v>6</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0.14884196999996599</v>
-      </c>
-      <c r="I8" s="1">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="K8" s="3">
-        <v>1.3060779999977901E-2</v>
-      </c>
-      <c r="L8" s="1">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="N8" s="3">
-        <v>0.144577089999984</v>
-      </c>
-      <c r="O8" s="1">
-        <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
+        <v>80000</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.18217882999999799</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.21871406000000199</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0.20816297000001199</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1.8133170000009999E-2</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.198631120000027</v>
+      </c>
+      <c r="I9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="O9" s="1"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B9" s="3">
-        <v>0.161532459999989</v>
-      </c>
-      <c r="C9">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10">
         <f t="shared" si="0"/>
-        <v>70</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0.185764670000025</v>
-      </c>
-      <c r="F9">
-        <v>7</v>
-      </c>
-      <c r="H9" s="3">
-        <v>0.17582784000001001</v>
-      </c>
-      <c r="I9" s="1">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="K9" s="3">
-        <v>1.5788879999990901E-2</v>
-      </c>
-      <c r="L9" s="1">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-      <c r="N9" s="3">
-        <v>0.170943110000007</v>
-      </c>
-      <c r="O9" s="1">
-        <f t="shared" si="3"/>
-        <v>7</v>
-      </c>
+        <v>90000</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0.205574060000003</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.24616752000001699</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0.231503059999977</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2.0086530000003201E-2</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0.22188695999998301</v>
+      </c>
+      <c r="I10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="O10" s="1"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B10" s="3">
-        <v>0.18217882999999799</v>
-      </c>
-      <c r="C10">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11">
         <f t="shared" si="0"/>
-        <v>80</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0.21871406000000199</v>
-      </c>
-      <c r="F10">
-        <v>8</v>
-      </c>
-      <c r="H10" s="3">
-        <v>0.20816297000001199</v>
-      </c>
-      <c r="I10" s="1">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="K10" s="3">
-        <v>1.8133170000009999E-2</v>
-      </c>
-      <c r="L10" s="1">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="N10" s="3">
-        <v>0.198631120000027</v>
-      </c>
-      <c r="O10" s="1">
-        <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
+        <v>100000</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0.23054614000000101</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.27831538999998801</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0.25898756000001399</v>
+      </c>
+      <c r="E11" s="3">
+        <v>2.2269469999991999E-2</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0.25193085999999298</v>
+      </c>
+      <c r="I11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="O11" s="1"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B11" s="3">
-        <v>0.205574060000003</v>
-      </c>
-      <c r="C11">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12">
         <f t="shared" si="0"/>
-        <v>90</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0.24616752000001699</v>
-      </c>
-      <c r="F11">
-        <v>9</v>
-      </c>
-      <c r="H11" s="3">
-        <v>0.231503059999977</v>
-      </c>
-      <c r="I11" s="1">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="K11" s="3">
-        <v>2.0086530000003201E-2</v>
-      </c>
-      <c r="L11" s="1">
-        <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-      <c r="N11" s="3">
-        <v>0.22188695999998301</v>
-      </c>
-      <c r="O11" s="1">
-        <f t="shared" si="3"/>
-        <v>9</v>
-      </c>
+        <v>110000</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0.25660143000000002</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.30960678000001202</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0.29222389999999898</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2.4458189999995699E-2</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0.28081431999999001</v>
+      </c>
+      <c r="I12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="O12" s="1"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B12" s="3">
-        <v>0.23054614000000101</v>
-      </c>
-      <c r="C12">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0.27831538999998801</v>
-      </c>
-      <c r="F12">
-        <v>10</v>
-      </c>
-      <c r="H12" s="3">
-        <v>0.25898756000001399</v>
-      </c>
-      <c r="I12" s="1">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="K12" s="3">
-        <v>2.2269469999991999E-2</v>
-      </c>
-      <c r="L12" s="1">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="N12" s="3">
-        <v>0.25193085999999298</v>
-      </c>
-      <c r="O12" s="1">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
+        <v>120000</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0.28242096000001299</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.33609983000001098</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0.32404839999999202</v>
+      </c>
+      <c r="E13" s="3">
+        <v>2.6438289999987302E-2</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0.30708472999999598</v>
+      </c>
+      <c r="I13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="O13" s="1"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B13" s="3">
-        <v>0.25660143000000002</v>
-      </c>
-      <c r="C13">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14">
         <f t="shared" si="0"/>
-        <v>110</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0.30960678000001202</v>
-      </c>
-      <c r="F13">
-        <v>11</v>
-      </c>
-      <c r="H13" s="3">
-        <v>0.29222389999999898</v>
-      </c>
-      <c r="I13" s="1">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="K13" s="3">
-        <v>2.4458189999995699E-2</v>
-      </c>
-      <c r="L13" s="1">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-      <c r="N13" s="3">
-        <v>0.28081431999999001</v>
-      </c>
-      <c r="O13" s="1">
-        <f t="shared" si="3"/>
-        <v>11</v>
-      </c>
+        <v>130000</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0.30764189999999803</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.36545630000000501</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0.34583521999998001</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2.8601709999998001E-2</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.33498862000001201</v>
+      </c>
+      <c r="I14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="O14" s="1"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B14" s="3">
-        <v>0.28242096000001299</v>
-      </c>
-      <c r="C14">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15">
         <f t="shared" si="0"/>
-        <v>120</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0.33609983000001098</v>
-      </c>
-      <c r="F14">
-        <v>12</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0.32404839999999202</v>
-      </c>
-      <c r="I14" s="1">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="K14" s="3">
-        <v>2.6438289999987302E-2</v>
-      </c>
-      <c r="L14" s="1">
-        <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0.30708472999999598</v>
-      </c>
-      <c r="O14" s="1">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
+        <v>140000</v>
+      </c>
+      <c r="B15" s="3">
+        <v>0.33841027999999301</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0.39749246000001198</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0.37981147999998899</v>
+      </c>
+      <c r="E15" s="3">
+        <v>3.0908799999997402E-2</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.365964450000001</v>
+      </c>
+      <c r="I15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="O15" s="1"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B15" s="3">
-        <v>0.30764189999999803</v>
-      </c>
-      <c r="C15">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16">
         <f t="shared" si="0"/>
-        <v>130</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0.36545630000000501</v>
-      </c>
-      <c r="F15">
-        <v>13</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0.34583521999998001</v>
-      </c>
-      <c r="I15" s="1">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="K15" s="3">
-        <v>2.8601709999998001E-2</v>
-      </c>
-      <c r="L15" s="1">
-        <f t="shared" si="2"/>
-        <v>13</v>
-      </c>
-      <c r="N15" s="3">
-        <v>0.33498862000001201</v>
-      </c>
-      <c r="O15" s="1">
-        <f t="shared" si="3"/>
-        <v>13</v>
-      </c>
+        <v>150000</v>
+      </c>
+      <c r="B16" s="3">
+        <v>0.36235713000000902</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0.43321334000001999</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0.40501946999997901</v>
+      </c>
+      <c r="E16" s="3">
+        <v>3.32464599999866E-2</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0.39184334000001397</v>
+      </c>
+      <c r="I16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="O16" s="1"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B16" s="3">
-        <v>0.33841027999999301</v>
-      </c>
-      <c r="C16">
-        <f t="shared" si="0"/>
-        <v>140</v>
-      </c>
-      <c r="E16" s="2">
-        <v>0.39749246000001198</v>
-      </c>
-      <c r="F16">
-        <v>14</v>
-      </c>
-      <c r="H16" s="3">
-        <v>0.37981147999998899</v>
-      </c>
-      <c r="I16" s="1">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="K16" s="3">
-        <v>3.0908799999997402E-2</v>
-      </c>
-      <c r="L16" s="1">
-        <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
-      <c r="N16" s="3">
-        <v>0.365964450000001</v>
-      </c>
-      <c r="O16" s="1">
-        <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B17" s="3">
-        <v>0.36235713000000902</v>
-      </c>
-      <c r="C17">
-        <f t="shared" si="0"/>
-        <v>150</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0.43321334000001999</v>
-      </c>
-      <c r="F17">
-        <f>F16+1</f>
-        <v>15</v>
-      </c>
-      <c r="H17" s="3">
-        <v>0.40501946999997901</v>
-      </c>
-      <c r="I17" s="1">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="K17" s="3">
-        <v>3.32464599999866E-2</v>
-      </c>
-      <c r="L17" s="1">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
-      <c r="N17" s="3">
-        <v>0.39184334000001397</v>
-      </c>
-      <c r="O17" s="1">
-        <f t="shared" si="3"/>
-        <v>15</v>
-      </c>
+    <row r="17" spans="9:15" x14ac:dyDescent="0.25">
+      <c r="I17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="O17" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9433,474 +9284,455 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47B6A206-9AEA-4BEF-B154-7845B567C9ED}">
-  <dimension ref="B1:O17"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" customWidth="1"/>
     <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1"/>
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="G1" s="1"/>
-      <c r="H1" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
-      <c r="K1" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-      <c r="N1" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>2</v>
-      </c>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>10000</v>
+      </c>
+      <c r="B2" s="3">
+        <v>2.0019500000034801E-2</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1.7841350000025999E-2</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1.8160039999975099E-2</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1.5653199999997001E-2</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1.6860090000000098E-2</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="2"/>
-      <c r="F3">
-        <v>1</v>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <f>A2+10^4</f>
+        <v>20000</v>
+      </c>
+      <c r="B3" s="3">
+        <v>4.1490420000036402E-2</v>
+      </c>
+      <c r="C3" s="2">
+        <v>3.7062779999996499E-2</v>
+      </c>
+      <c r="D3" s="3">
+        <v>3.73390899999776E-2</v>
+      </c>
+      <c r="E3" s="2">
+        <v>3.1338310000001E-2</v>
+      </c>
+      <c r="F3" s="2">
+        <v>3.24042599999756E-2</v>
       </c>
       <c r="H3" s="3"/>
-      <c r="I3" s="1">
-        <v>1</v>
-      </c>
+      <c r="I3" s="1"/>
       <c r="K3" s="3"/>
-      <c r="L3" s="1">
-        <v>1</v>
-      </c>
+      <c r="L3" s="1"/>
       <c r="N3" s="3"/>
-      <c r="O3" s="1">
-        <v>1</v>
-      </c>
+      <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B4" s="3"/>
-      <c r="C4">
-        <f>C3+1</f>
-        <v>2</v>
-      </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="2"/>
-      <c r="F4">
-        <f>F3+1</f>
-        <v>2</v>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <f t="shared" ref="A4:A16" si="0">A3+10^4</f>
+        <v>30000</v>
+      </c>
+      <c r="B4" s="3">
+        <v>6.4305039999999203E-2</v>
+      </c>
+      <c r="C4" s="2">
+        <v>5.86902699999882E-2</v>
+      </c>
+      <c r="D4" s="3">
+        <v>5.8605320000015101E-2</v>
+      </c>
+      <c r="E4" s="2">
+        <v>5.1110870000002202E-2</v>
+      </c>
+      <c r="F4" s="2">
+        <v>5.4209910000008597E-2</v>
       </c>
       <c r="H4" s="3"/>
-      <c r="I4" s="1">
-        <f>I3+1</f>
-        <v>2</v>
-      </c>
+      <c r="I4" s="1"/>
       <c r="K4" s="3"/>
-      <c r="L4" s="1">
-        <f>L3+1</f>
-        <v>2</v>
-      </c>
+      <c r="L4" s="1"/>
       <c r="N4" s="3"/>
-      <c r="O4" s="1">
-        <f>O3+1</f>
-        <v>2</v>
-      </c>
+      <c r="O4" s="1"/>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B5" s="3"/>
-      <c r="C5">
-        <f t="shared" ref="C5:C17" si="0">C4+1</f>
-        <v>3</v>
-      </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="2"/>
-      <c r="F5">
-        <v>3</v>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <f t="shared" si="0"/>
+        <v>40000</v>
+      </c>
+      <c r="B5" s="3">
+        <v>8.6936269999978305E-2</v>
+      </c>
+      <c r="C5" s="2">
+        <v>8.0023600000003997E-2</v>
+      </c>
+      <c r="D5" s="3">
+        <v>7.9978059999984905E-2</v>
+      </c>
+      <c r="E5" s="2">
+        <v>7.0834349999995494E-2</v>
+      </c>
+      <c r="F5" s="2">
+        <v>7.4716889999990599E-2</v>
       </c>
       <c r="H5" s="3"/>
-      <c r="I5" s="1">
-        <f t="shared" ref="I5:I17" si="1">I4+1</f>
-        <v>3</v>
-      </c>
+      <c r="I5" s="1"/>
       <c r="K5" s="3"/>
-      <c r="L5" s="1">
-        <f t="shared" ref="L5:L17" si="2">L4+1</f>
-        <v>3</v>
-      </c>
+      <c r="L5" s="1"/>
       <c r="N5" s="3"/>
-      <c r="O5" s="1">
-        <f t="shared" ref="O5:O17" si="3">O4+1</f>
-        <v>3</v>
-      </c>
+      <c r="O5" s="1"/>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B6" s="3"/>
-      <c r="C6">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="2"/>
-      <c r="F6">
-        <v>4</v>
+        <v>50000</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0.108763700000008</v>
+      </c>
+      <c r="C6" s="2">
+        <v>9.9360209999986099E-2</v>
+      </c>
+      <c r="D6" s="3">
+        <v>9.9421810000012503E-2</v>
+      </c>
+      <c r="E6" s="2">
+        <v>8.4614740000006294E-2</v>
+      </c>
+      <c r="F6" s="2">
+        <v>9.1542620000018296E-2</v>
       </c>
       <c r="H6" s="3"/>
-      <c r="I6" s="1">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
+      <c r="I6" s="1"/>
       <c r="K6" s="3"/>
-      <c r="L6" s="1">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
+      <c r="L6" s="1"/>
       <c r="N6" s="3"/>
-      <c r="O6" s="1">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
+      <c r="O6" s="1"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B7" s="3"/>
-      <c r="C7">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="2"/>
-      <c r="F7">
-        <v>5</v>
+        <v>60000</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0.13077272000000401</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.119507720000001</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.12010453000002599</v>
+      </c>
+      <c r="E7" s="2">
+        <v>9.9418790000026999E-2</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.106035139999994</v>
       </c>
       <c r="H7" s="3"/>
-      <c r="I7" s="1">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
+      <c r="I7" s="1"/>
       <c r="K7" s="3"/>
-      <c r="L7" s="1">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
+      <c r="L7" s="1"/>
       <c r="N7" s="3"/>
-      <c r="O7" s="1">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
+      <c r="O7" s="1"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B8" s="3"/>
-      <c r="C8">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="2"/>
-      <c r="F8">
-        <v>6</v>
+        <v>70000</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0.15336612999999399</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.14486256999998601</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.14226474000001799</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0.117413970000006</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.12621419000001799</v>
       </c>
       <c r="H8" s="3"/>
-      <c r="I8" s="1">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
+      <c r="I8" s="1"/>
       <c r="K8" s="3"/>
-      <c r="L8" s="1">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
+      <c r="L8" s="1"/>
       <c r="N8" s="3"/>
-      <c r="O8" s="1">
-        <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
+      <c r="O8" s="1"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B9" s="3"/>
-      <c r="C9">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9">
         <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="2"/>
-      <c r="F9">
-        <v>7</v>
+        <v>80000</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.17732276000001501</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.162076529999967</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0.164695030000029</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0.134773660000018</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.14530125999999599</v>
       </c>
       <c r="H9" s="3"/>
-      <c r="I9" s="1">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
+      <c r="I9" s="1"/>
       <c r="K9" s="3"/>
-      <c r="L9" s="1">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
+      <c r="L9" s="1"/>
       <c r="N9" s="3"/>
-      <c r="O9" s="1">
-        <f t="shared" si="3"/>
-        <v>7</v>
-      </c>
+      <c r="O9" s="1"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B10" s="3"/>
-      <c r="C10">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10">
         <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="D10" s="1"/>
-      <c r="E10" s="2"/>
-      <c r="F10">
-        <v>8</v>
+        <v>90000</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0.20086420999996299</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.18628506999998501</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0.18702865000000199</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0.154947579999998</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.16312177999998301</v>
       </c>
       <c r="H10" s="3"/>
-      <c r="I10" s="1">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
+      <c r="I10" s="1"/>
       <c r="K10" s="3"/>
-      <c r="L10" s="1">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
+      <c r="L10" s="1"/>
       <c r="N10" s="3"/>
-      <c r="O10" s="1">
-        <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
+      <c r="O10" s="1"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B11" s="3"/>
-      <c r="C11">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="2"/>
-      <c r="F11">
-        <v>9</v>
+        <v>100000</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0.224657350000006</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.20845273999998401</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0.20919062999996599</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0.170236430000022</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.18419293000001699</v>
       </c>
       <c r="H11" s="3"/>
-      <c r="I11" s="1">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
+      <c r="I11" s="1"/>
       <c r="K11" s="3"/>
-      <c r="L11" s="1">
-        <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
+      <c r="L11" s="1"/>
       <c r="N11" s="3"/>
-      <c r="O11" s="1">
-        <f t="shared" si="3"/>
-        <v>9</v>
-      </c>
+      <c r="O11" s="1"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B12" s="3"/>
-      <c r="C12">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
-      <c r="F12">
-        <v>10</v>
+        <v>110000</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0.24952613999998899</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.22946242999996599</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0.229304070000034</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0.18890194000000499</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.210099190000028</v>
       </c>
       <c r="H12" s="3"/>
-      <c r="I12" s="1">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
+      <c r="I12" s="1"/>
       <c r="K12" s="3"/>
-      <c r="L12" s="1">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
+      <c r="L12" s="1"/>
       <c r="N12" s="3"/>
-      <c r="O12" s="1">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
+      <c r="O12" s="1"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B13" s="3"/>
-      <c r="C13">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="2"/>
-      <c r="F13">
-        <v>11</v>
+        <v>120000</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0.27439481999999699</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.24798472999996099</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0.24864232999998401</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0.20853489000000899</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.240699289999975</v>
       </c>
       <c r="H13" s="3"/>
-      <c r="I13" s="1">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
+      <c r="I13" s="1"/>
       <c r="K13" s="3"/>
-      <c r="L13" s="1">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
+      <c r="L13" s="1"/>
       <c r="N13" s="3"/>
-      <c r="O13" s="1">
-        <f t="shared" si="3"/>
-        <v>11</v>
-      </c>
+      <c r="O13" s="1"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B14" s="3"/>
-      <c r="C14">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14">
         <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="D14" s="1"/>
-      <c r="E14" s="2"/>
-      <c r="F14">
-        <v>12</v>
+        <v>130000</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0.29654835000001101</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.26957318999998198</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0.27238376999998698</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0.22714252000000601</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.25257817999999999</v>
       </c>
       <c r="H14" s="3"/>
-      <c r="I14" s="1">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
+      <c r="I14" s="1"/>
       <c r="K14" s="3"/>
-      <c r="L14" s="1">
-        <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
+      <c r="L14" s="1"/>
       <c r="N14" s="3"/>
-      <c r="O14" s="1">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
+      <c r="O14" s="1"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B15" s="3"/>
-      <c r="C15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15">
         <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="D15" s="1"/>
-      <c r="E15" s="2"/>
-      <c r="F15">
-        <v>13</v>
+        <v>140000</v>
+      </c>
+      <c r="B15" s="3">
+        <v>0.32133721999998599</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0.29025454000002299</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0.294165449999991</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0.245429439999998</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.27556503999999199</v>
       </c>
       <c r="H15" s="3"/>
-      <c r="I15" s="1">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
+      <c r="I15" s="1"/>
       <c r="K15" s="3"/>
-      <c r="L15" s="1">
-        <f t="shared" si="2"/>
-        <v>13</v>
-      </c>
+      <c r="L15" s="1"/>
       <c r="N15" s="3"/>
-      <c r="O15" s="1">
-        <f t="shared" si="3"/>
-        <v>13</v>
-      </c>
+      <c r="O15" s="1"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B16" s="3"/>
-      <c r="C16">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="D16" s="1"/>
-      <c r="E16" s="2"/>
-      <c r="F16">
-        <v>14</v>
+        <v>150000</v>
+      </c>
+      <c r="B16" s="3">
+        <v>0.346233530000017</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0.31542898000002401</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0.31352213999998602</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.26384250000000897</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.29787633000000802</v>
       </c>
       <c r="H16" s="3"/>
-      <c r="I16" s="1">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
+      <c r="I16" s="1"/>
       <c r="K16" s="3"/>
-      <c r="L16" s="1">
-        <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
+      <c r="L16" s="1"/>
       <c r="N16" s="3"/>
-      <c r="O16" s="1">
-        <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
+      <c r="O16" s="1"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B17" s="3"/>
-      <c r="C17">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
       <c r="D17" s="1"/>
       <c r="E17" s="2"/>
-      <c r="F17">
-        <f>F16+1</f>
-        <v>15</v>
-      </c>
       <c r="H17" s="3"/>
-      <c r="I17" s="1">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
+      <c r="I17" s="1"/>
       <c r="K17" s="3"/>
-      <c r="L17" s="1">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
+      <c r="L17" s="1"/>
       <c r="N17" s="3"/>
-      <c r="O17" s="1">
-        <f t="shared" si="3"/>
-        <v>15</v>
-      </c>
+      <c r="O17" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9910,374 +9742,266 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{392EA1D7-C2F5-42EB-A403-289E61C008A4}">
-  <dimension ref="B1:O17"/>
+  <dimension ref="B1:O19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1">
+        <v>100</v>
+      </c>
+      <c r="E1">
+        <v>200</v>
+      </c>
+      <c r="F1">
+        <v>300</v>
+      </c>
+      <c r="G1">
+        <v>400</v>
+      </c>
+      <c r="H1">
+        <v>500</v>
+      </c>
+      <c r="I1">
+        <v>600</v>
+      </c>
+      <c r="J1">
+        <v>700</v>
+      </c>
+      <c r="K1">
+        <v>800</v>
+      </c>
+      <c r="L1">
+        <v>900</v>
+      </c>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
     <row r="2" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
+      <c r="D2" s="4">
+        <v>7.17330002225935E-4</v>
+      </c>
+      <c r="E2" s="4">
+        <v>7.4334999953862204E-4</v>
+      </c>
+      <c r="F2" s="4">
+        <v>9.5708000008016799E-4</v>
+      </c>
+      <c r="G2" s="4">
+        <v>1.0421999992104201E-3</v>
+      </c>
+      <c r="H2" s="4">
+        <v>1.2964599998667801E-3</v>
+      </c>
+      <c r="I2" s="4">
+        <v>1.4042499999049999E-3</v>
+      </c>
+      <c r="J2" s="4">
+        <v>1.4908999990439001E-3</v>
+      </c>
+      <c r="K2" s="4">
+        <v>1.55782999936491E-3</v>
+      </c>
+      <c r="L2" s="4">
+        <v>1.6475899989018201E-3</v>
+      </c>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3">
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="2"/>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="1">
-        <v>1</v>
-      </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="1"/>
+      <c r="D3" s="5">
+        <v>2.3945000139065001E-4</v>
+      </c>
+      <c r="E3" s="5">
+        <v>6.1512999818660299E-4</v>
+      </c>
+      <c r="F3" s="5">
+        <v>1.2178900011349399E-3</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1.9513399980496599E-3</v>
+      </c>
+      <c r="H3" s="5">
+        <v>3.0918299977201898E-3</v>
+      </c>
+      <c r="I3" s="5">
+        <v>4.4002500013448301E-3</v>
+      </c>
+      <c r="J3" s="5">
+        <v>6.1177800002042201E-3</v>
+      </c>
+      <c r="K3" s="5">
+        <v>7.4757599999429603E-3</v>
+      </c>
+      <c r="L3" s="5">
+        <v>9.1746099991723892E-3</v>
+      </c>
       <c r="N3" s="3"/>
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B4" s="3"/>
-      <c r="C4">
-        <f>C3+1</f>
-        <v>2</v>
-      </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="2"/>
-      <c r="F4">
-        <f>F3+1</f>
-        <v>2</v>
-      </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="1">
-        <f>I3+1</f>
-        <v>2</v>
-      </c>
-      <c r="K4" s="3"/>
-      <c r="L4" s="1"/>
+      <c r="B4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5">
+        <v>4.4845999800600098E-4</v>
+      </c>
+      <c r="E4" s="5">
+        <v>1.0656999977072699E-3</v>
+      </c>
+      <c r="F4" s="5">
+        <v>2.3012400022707799E-3</v>
+      </c>
+      <c r="G4" s="5">
+        <v>4.0465000027324997E-3</v>
+      </c>
+      <c r="H4" s="5">
+        <v>5.8049900020705498E-3</v>
+      </c>
+      <c r="I4" s="5">
+        <v>8.4697399986907798E-3</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1.1194689999683699E-2</v>
+      </c>
+      <c r="K4" s="4">
+        <v>1.4471140000387E-2</v>
+      </c>
+      <c r="L4" s="4">
+        <v>1.83346799982246E-2</v>
+      </c>
       <c r="N4" s="3"/>
       <c r="O4" s="1"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
-      <c r="C5">
-        <f t="shared" ref="C5:C17" si="0">C4+1</f>
-        <v>3</v>
-      </c>
-      <c r="D5" s="1"/>
       <c r="E5" s="2"/>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="1">
-        <f t="shared" ref="I5:I17" si="1">I4+1</f>
-        <v>3</v>
-      </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="1"/>
-      <c r="N5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="1"/>
       <c r="O5" s="1"/>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B6" s="3"/>
-      <c r="C6">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="D6" s="1"/>
       <c r="E6" s="2"/>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="1">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="K6" s="3"/>
-      <c r="L6" s="1"/>
-      <c r="N6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B7" s="3"/>
-      <c r="C7">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="D7" s="1"/>
       <c r="E7" s="2"/>
-      <c r="F7">
-        <v>5</v>
-      </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="1">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="K7" s="3"/>
-      <c r="L7" s="1"/>
-      <c r="N7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="1"/>
       <c r="O7" s="1"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B8" s="3"/>
-      <c r="C8">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="D8" s="1"/>
       <c r="E8" s="2"/>
-      <c r="F8">
-        <v>6</v>
-      </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="1">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="K8" s="3"/>
-      <c r="L8" s="1"/>
-      <c r="N8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="1"/>
       <c r="O8" s="1"/>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" s="3"/>
-      <c r="C9">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="D9" s="1"/>
       <c r="E9" s="2"/>
-      <c r="F9">
-        <v>7</v>
-      </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="1">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="K9" s="3"/>
-      <c r="L9" s="1"/>
-      <c r="N9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="1"/>
       <c r="O9" s="1"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10" s="3"/>
-      <c r="C10">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="D10" s="1"/>
       <c r="E10" s="2"/>
-      <c r="F10">
-        <v>8</v>
-      </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="1">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="K10" s="3"/>
-      <c r="L10" s="1"/>
-      <c r="N10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="1"/>
       <c r="O10" s="1"/>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B11" s="3"/>
-      <c r="C11">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="D11" s="1"/>
       <c r="E11" s="2"/>
-      <c r="F11">
-        <v>9</v>
-      </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="1">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="K11" s="3"/>
-      <c r="L11" s="1"/>
-      <c r="N11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="1"/>
       <c r="O11" s="1"/>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12" s="3"/>
-      <c r="C12">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="D12" s="1"/>
       <c r="E12" s="2"/>
-      <c r="F12">
-        <v>10</v>
-      </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="1">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="K12" s="3"/>
-      <c r="L12" s="1"/>
-      <c r="N12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="1"/>
       <c r="O12" s="1"/>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B13" s="3"/>
-      <c r="C13">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
       <c r="D13" s="1"/>
       <c r="E13" s="2"/>
-      <c r="F13">
-        <v>11</v>
-      </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="1">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="K13" s="3"/>
-      <c r="L13" s="1"/>
-      <c r="N13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="1"/>
       <c r="O13" s="1"/>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B14" s="3"/>
-      <c r="C14">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
       <c r="D14" s="1"/>
       <c r="E14" s="2"/>
-      <c r="F14">
-        <v>12</v>
-      </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="1">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="K14" s="3"/>
-      <c r="L14" s="1"/>
-      <c r="N14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="1"/>
       <c r="O14" s="1"/>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B15" s="3"/>
-      <c r="C15">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
       <c r="D15" s="1"/>
       <c r="E15" s="2"/>
-      <c r="F15">
-        <v>13</v>
-      </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="1">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="K15" s="3"/>
-      <c r="L15" s="1"/>
-      <c r="N15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="1"/>
       <c r="O15" s="1"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B16" s="3"/>
-      <c r="C16">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
       <c r="D16" s="1"/>
       <c r="E16" s="2"/>
-      <c r="F16">
-        <v>14</v>
-      </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="1">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="K16" s="3"/>
-      <c r="L16" s="1"/>
-      <c r="N16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="1"/>
       <c r="O16" s="1"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B17" s="3"/>
-      <c r="C17">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
       <c r="D17" s="1"/>
       <c r="E17" s="2"/>
-      <c r="F17">
-        <f>F16+1</f>
-        <v>15</v>
-      </c>
-      <c r="H17" s="3"/>
-      <c r="I17" s="1">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="K17" s="3"/>
-      <c r="L17" s="1"/>
-      <c r="N17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="1"/>
       <c r="O17" s="1"/>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="M18" s="3"/>
+      <c r="N18" s="1"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="M19" s="3"/>
+      <c r="N19" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Wykresy.xlsx
+++ b/Wykresy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\studia_aisd\algorytmy_sortowania\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22F43043-C8AA-4722-96F9-E65B122C46EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ADE4DA0-EDBF-4A6D-A987-8B7D7DEB1143}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{19E7D5CD-98A1-451F-9163-D7D48B512516}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{19E7D5CD-98A1-451F-9163-D7D48B512516}"/>
   </bookViews>
   <sheets>
     <sheet name="IS" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.00000"/>
-    <numFmt numFmtId="169" formatCode="0.0000000"/>
+    <numFmt numFmtId="165" formatCode="0.0000000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -104,15 +104,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -150,6 +148,31 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pl-PL"/>
+              <a:t>IS</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1203,7 +1226,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="00B0F0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1273,49 +1296,49 @@
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.29711640000004902</c:v>
+                  <c:v>0.25781388333340699</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.42092019999972702</c:v>
+                  <c:v>0.37203773333339901</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.56643490000033103</c:v>
+                  <c:v>0.50703355000011097</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.689637999999831</c:v>
+                  <c:v>0.630570799999986</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.93152640000016596</c:v>
+                  <c:v>0.79793708333333202</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.1448983999998701</c:v>
+                  <c:v>0.98203875000005303</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.2892377000002799</c:v>
+                  <c:v>1.1918108500000599</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.6510609000001699</c:v>
+                  <c:v>1.41606359999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.7719887000002901</c:v>
+                  <c:v>1.65773588333331</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.23256409999976</c:v>
+                  <c:v>1.9239119833334</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.5738467999999499</c:v>
+                  <c:v>2.20436368333336</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.7353607000000002</c:v>
+                  <c:v>2.5126235833332999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.3449150000001202</c:v>
+                  <c:v>2.8577134166666802</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.40162020000025</c:v>
+                  <c:v>3.20324408333332</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>4.11404940000011</c:v>
+                  <c:v>3.5692949500000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1414,49 +1437,49 @@
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.27801170000020597</c:v>
+                  <c:v>0.27572288333324901</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.39111229999980401</c:v>
+                  <c:v>0.376129916666741</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.561001900000064</c:v>
+                  <c:v>0.51118318333328705</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.92349749999993902</c:v>
+                  <c:v>0.66726523333333398</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.86902899999995498</c:v>
+                  <c:v>0.91959028333333903</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.10183499999993</c:v>
+                  <c:v>1.0811677333332801</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.3148572000000001</c:v>
+                  <c:v>1.37285360000002</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.5503923000001101</c:v>
+                  <c:v>1.62106919999996</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.8155158999998</c:v>
+                  <c:v>1.8680017833332001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.7273538999997902</c:v>
+                  <c:v>2.15672694999996</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.35320389999969</c:v>
+                  <c:v>2.4655252166667099</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.7455755999999298</c:v>
+                  <c:v>2.7190607833334299</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.0529510999999698</c:v>
+                  <c:v>3.0772922666666598</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.44943740000007</c:v>
+                  <c:v>3.51721174999996</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3.81637829999999</c:v>
+                  <c:v>3.8006664833333099</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1555,49 +1578,49 @@
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.371550500000012</c:v>
+                  <c:v>0.27786156666661499</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.404069400000025</c:v>
+                  <c:v>0.38898889999988201</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.56454829999984202</c:v>
+                  <c:v>0.52904913333319803</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.73407259999976304</c:v>
+                  <c:v>0.691831849999895</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.92283070000030398</c:v>
+                  <c:v>0.87640433333338696</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.1276714999999</c:v>
+                  <c:v>1.08015643333328</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.77930940000032</c:v>
+                  <c:v>1.3029282333333501</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.6312573999998601</c:v>
+                  <c:v>1.5501980333333401</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.89283960000011</c:v>
+                  <c:v>1.82429523333333</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.1945440000004002</c:v>
+                  <c:v>2.1265790833334299</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.50375829999984</c:v>
+                  <c:v>2.4339064499999901</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.8445698000000399</c:v>
+                  <c:v>2.7286221500000098</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>4.2412036000000599</c:v>
+                  <c:v>3.1502399666666498</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.6253870999998901</c:v>
+                  <c:v>3.5464354999999101</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>4.1029728000003098</c:v>
+                  <c:v>3.9288310000000202</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1696,49 +1719,49 @@
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.26314849999971501</c:v>
+                  <c:v>0.268659616666658</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.37396750000016199</c:v>
+                  <c:v>0.37027448333340801</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.529808199999934</c:v>
+                  <c:v>0.52617856666665797</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.71018950000006897</c:v>
+                  <c:v>0.67876736666660997</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.84070620000011298</c:v>
+                  <c:v>0.82115553333323898</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0199678999997499</c:v>
+                  <c:v>1.00970286666673</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.24446809999972</c:v>
+                  <c:v>1.2266212166667401</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.49062700000013</c:v>
+                  <c:v>1.47981385000002</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.77890509999997</c:v>
+                  <c:v>1.68888911666666</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.02817709999999</c:v>
+                  <c:v>1.96121579999999</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.3299543999996701</c:v>
+                  <c:v>2.2439728999999402</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.6098971999999701</c:v>
+                  <c:v>2.56352223333336</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.99417149999999</c:v>
+                  <c:v>2.9128057999999601</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.33117489999995</c:v>
+                  <c:v>3.2378344833333901</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3.7084792000000499</c:v>
+                  <c:v>3.6026052166665301</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1767,7 +1790,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent5"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1837,49 +1860,49 @@
                 <c:formatCode>0.00000</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.29711640000004902</c:v>
+                  <c:v>0.30339944999999102</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.42092019999972702</c:v>
+                  <c:v>0.39276484999997202</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.56643490000033103</c:v>
+                  <c:v>0.56112846666671101</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.689637999999831</c:v>
+                  <c:v>0.69542756666654204</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.93152640000016596</c:v>
+                  <c:v>0.92404061666654003</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.1448983999998701</c:v>
+                  <c:v>1.1905391166666599</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.2892377000002799</c:v>
+                  <c:v>1.4369615999998999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.6510609000001699</c:v>
+                  <c:v>1.6362872333332501</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.7719887000002901</c:v>
+                  <c:v>1.98379481666658</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.23256409999976</c:v>
+                  <c:v>2.2264519666665898</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.5738467999999499</c:v>
+                  <c:v>2.5567930833332499</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.7353607000000002</c:v>
+                  <c:v>2.91989296666664</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.3449150000001202</c:v>
+                  <c:v>3.32174546666662</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.40162020000025</c:v>
+                  <c:v>3.6998055166667001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>4.11404940000011</c:v>
+                  <c:v>4.2211402500000297</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4469,7 +4492,7 @@
             <c:numRef>
               <c:f>QS!$D$4:$L$4</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0000000</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>4.4845999800600098E-4</c:v>
@@ -8049,7 +8072,7 @@
       <c r="D2">
         <v>0.57234600000037905</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2">
         <v>3.9689999994152399E-4</v>
       </c>
       <c r="F2">
@@ -8075,7 +8098,7 @@
       <c r="D3">
         <v>0.87804570000025695</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="2">
         <v>4.6110000039334398E-4</v>
       </c>
       <c r="F3">
@@ -8101,7 +8124,7 @@
       <c r="D4">
         <v>1.13276829999995</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="2">
         <v>5.3290000005290397E-4</v>
       </c>
       <c r="F4">
@@ -8127,7 +8150,7 @@
       <c r="D5">
         <v>1.42819370000006</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="2">
         <v>6.5750000021580404E-4</v>
       </c>
       <c r="F5">
@@ -8153,7 +8176,7 @@
       <c r="D6">
         <v>1.8054827000000799</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="2">
         <v>7.1089999983087095E-4</v>
       </c>
       <c r="F6">
@@ -8179,7 +8202,7 @@
       <c r="D7">
         <v>2.2503299999998401</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="2">
         <v>7.6600000011239899E-4</v>
       </c>
       <c r="F7">
@@ -8205,7 +8228,7 @@
       <c r="D8">
         <v>2.7179971000000398</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="2">
         <v>8.4030000016355102E-4</v>
       </c>
       <c r="F8">
@@ -8231,7 +8254,7 @@
       <c r="D9">
         <v>3.1981657000001098</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="2">
         <v>9.7079999977722699E-4</v>
       </c>
       <c r="F9">
@@ -8257,7 +8280,7 @@
       <c r="D10">
         <v>3.7459339000001801</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="2">
         <v>1.17610000006607E-3</v>
       </c>
       <c r="F10">
@@ -8283,7 +8306,7 @@
       <c r="D11">
         <v>4.4209681000002004</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="2">
         <v>1.0643999999047E-3</v>
       </c>
       <c r="F11">
@@ -8309,7 +8332,7 @@
       <c r="D12">
         <v>5.0299622999996201</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="2">
         <v>1.2022999999317099E-3</v>
       </c>
       <c r="F12">
@@ -8335,7 +8358,7 @@
       <c r="D13">
         <v>5.7007025000002596</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="2">
         <v>1.2292999999772201E-3</v>
       </c>
       <c r="F13">
@@ -8361,7 +8384,7 @@
       <c r="D14">
         <v>6.49658449999969</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="2">
         <v>1.3216000002103101E-3</v>
       </c>
       <c r="F14">
@@ -8387,7 +8410,7 @@
       <c r="D15">
         <v>7.2027017999998799</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="2">
         <v>1.3784000002488E-3</v>
       </c>
       <c r="F15">
@@ -8413,7 +8436,7 @@
       <c r="D16">
         <v>8.0657694000001303</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="2">
         <v>1.6263000002254501E-3</v>
       </c>
       <c r="F16">
@@ -8483,19 +8506,19 @@
         <v>5000</v>
       </c>
       <c r="B2" s="3">
-        <v>0.29711640000004902</v>
+        <v>0.25781388333340699</v>
       </c>
       <c r="C2" s="2">
-        <v>0.27801170000020597</v>
+        <v>0.27572288333324901</v>
       </c>
       <c r="D2" s="2">
-        <v>0.371550500000012</v>
+        <v>0.27786156666661499</v>
       </c>
       <c r="E2" s="2">
-        <v>0.26314849999971501</v>
+        <v>0.268659616666658</v>
       </c>
       <c r="F2" s="2">
-        <v>0.29711640000004902</v>
+        <v>0.30339944999999102</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -8509,19 +8532,19 @@
         <v>6000</v>
       </c>
       <c r="B3" s="3">
-        <v>0.42092019999972702</v>
+        <v>0.37203773333339901</v>
       </c>
       <c r="C3" s="2">
-        <v>0.39111229999980401</v>
+        <v>0.376129916666741</v>
       </c>
       <c r="D3" s="2">
-        <v>0.404069400000025</v>
+        <v>0.38898889999988201</v>
       </c>
       <c r="E3" s="2">
-        <v>0.37396750000016199</v>
+        <v>0.37027448333340801</v>
       </c>
       <c r="F3" s="2">
-        <v>0.42092019999972702</v>
+        <v>0.39276484999997202</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="1"/>
@@ -8535,19 +8558,19 @@
         <v>7000</v>
       </c>
       <c r="B4" s="3">
-        <v>0.56643490000033103</v>
+        <v>0.50703355000011097</v>
       </c>
       <c r="C4" s="2">
-        <v>0.561001900000064</v>
+        <v>0.51118318333328705</v>
       </c>
       <c r="D4" s="2">
-        <v>0.56454829999984202</v>
+        <v>0.52904913333319803</v>
       </c>
       <c r="E4" s="2">
-        <v>0.529808199999934</v>
+        <v>0.52617856666665797</v>
       </c>
       <c r="F4" s="2">
-        <v>0.56643490000033103</v>
+        <v>0.56112846666671101</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="1"/>
@@ -8561,19 +8584,19 @@
         <v>8000</v>
       </c>
       <c r="B5" s="3">
-        <v>0.689637999999831</v>
+        <v>0.630570799999986</v>
       </c>
       <c r="C5" s="2">
-        <v>0.92349749999993902</v>
+        <v>0.66726523333333398</v>
       </c>
       <c r="D5" s="2">
-        <v>0.73407259999976304</v>
+        <v>0.691831849999895</v>
       </c>
       <c r="E5" s="2">
-        <v>0.71018950000006897</v>
+        <v>0.67876736666660997</v>
       </c>
       <c r="F5" s="2">
-        <v>0.689637999999831</v>
+        <v>0.69542756666654204</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="1"/>
@@ -8587,19 +8610,19 @@
         <v>9000</v>
       </c>
       <c r="B6" s="3">
-        <v>0.93152640000016596</v>
+        <v>0.79793708333333202</v>
       </c>
       <c r="C6" s="2">
-        <v>0.86902899999995498</v>
+        <v>0.91959028333333903</v>
       </c>
       <c r="D6" s="2">
-        <v>0.92283070000030398</v>
+        <v>0.87640433333338696</v>
       </c>
       <c r="E6" s="2">
-        <v>0.84070620000011298</v>
+        <v>0.82115553333323898</v>
       </c>
       <c r="F6" s="2">
-        <v>0.93152640000016596</v>
+        <v>0.92404061666654003</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="1"/>
@@ -8613,19 +8636,19 @@
         <v>10000</v>
       </c>
       <c r="B7" s="3">
-        <v>1.1448983999998701</v>
+        <v>0.98203875000005303</v>
       </c>
       <c r="C7" s="2">
-        <v>1.10183499999993</v>
+        <v>1.0811677333332801</v>
       </c>
       <c r="D7" s="2">
-        <v>1.1276714999999</v>
+        <v>1.08015643333328</v>
       </c>
       <c r="E7" s="2">
-        <v>1.0199678999997499</v>
+        <v>1.00970286666673</v>
       </c>
       <c r="F7" s="2">
-        <v>1.1448983999998701</v>
+        <v>1.1905391166666599</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="1"/>
@@ -8639,19 +8662,19 @@
         <v>11000</v>
       </c>
       <c r="B8" s="3">
-        <v>1.2892377000002799</v>
+        <v>1.1918108500000599</v>
       </c>
       <c r="C8" s="2">
-        <v>1.3148572000000001</v>
+        <v>1.37285360000002</v>
       </c>
       <c r="D8" s="2">
-        <v>1.77930940000032</v>
+        <v>1.3029282333333501</v>
       </c>
       <c r="E8" s="2">
-        <v>1.24446809999972</v>
+        <v>1.2266212166667401</v>
       </c>
       <c r="F8" s="2">
-        <v>1.2892377000002799</v>
+        <v>1.4369615999998999</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="1"/>
@@ -8665,19 +8688,19 @@
         <v>12000</v>
       </c>
       <c r="B9" s="3">
-        <v>1.6510609000001699</v>
+        <v>1.41606359999999</v>
       </c>
       <c r="C9" s="2">
-        <v>1.5503923000001101</v>
+        <v>1.62106919999996</v>
       </c>
       <c r="D9" s="2">
-        <v>1.6312573999998601</v>
+        <v>1.5501980333333401</v>
       </c>
       <c r="E9" s="2">
-        <v>1.49062700000013</v>
+        <v>1.47981385000002</v>
       </c>
       <c r="F9" s="2">
-        <v>1.6510609000001699</v>
+        <v>1.6362872333332501</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="1"/>
@@ -8691,19 +8714,19 @@
         <v>13000</v>
       </c>
       <c r="B10" s="3">
-        <v>1.7719887000002901</v>
+        <v>1.65773588333331</v>
       </c>
       <c r="C10" s="2">
-        <v>1.8155158999998</v>
+        <v>1.8680017833332001</v>
       </c>
       <c r="D10" s="2">
-        <v>1.89283960000011</v>
+        <v>1.82429523333333</v>
       </c>
       <c r="E10" s="2">
-        <v>1.77890509999997</v>
+        <v>1.68888911666666</v>
       </c>
       <c r="F10" s="2">
-        <v>1.7719887000002901</v>
+        <v>1.98379481666658</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="1"/>
@@ -8717,19 +8740,19 @@
         <v>14000</v>
       </c>
       <c r="B11" s="3">
-        <v>2.23256409999976</v>
+        <v>1.9239119833334</v>
       </c>
       <c r="C11" s="2">
-        <v>2.7273538999997902</v>
+        <v>2.15672694999996</v>
       </c>
       <c r="D11" s="2">
-        <v>2.1945440000004002</v>
+        <v>2.1265790833334299</v>
       </c>
       <c r="E11" s="2">
-        <v>2.02817709999999</v>
+        <v>1.96121579999999</v>
       </c>
       <c r="F11" s="2">
-        <v>2.23256409999976</v>
+        <v>2.2264519666665898</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="1"/>
@@ -8743,19 +8766,19 @@
         <v>15000</v>
       </c>
       <c r="B12" s="3">
-        <v>2.5738467999999499</v>
+        <v>2.20436368333336</v>
       </c>
       <c r="C12" s="2">
-        <v>2.35320389999969</v>
+        <v>2.4655252166667099</v>
       </c>
       <c r="D12" s="2">
-        <v>2.50375829999984</v>
+        <v>2.4339064499999901</v>
       </c>
       <c r="E12" s="2">
-        <v>2.3299543999996701</v>
+        <v>2.2439728999999402</v>
       </c>
       <c r="F12" s="2">
-        <v>2.5738467999999499</v>
+        <v>2.5567930833332499</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="1"/>
@@ -8769,19 +8792,19 @@
         <v>16000</v>
       </c>
       <c r="B13" s="3">
-        <v>2.7353607000000002</v>
+        <v>2.5126235833332999</v>
       </c>
       <c r="C13" s="2">
-        <v>2.7455755999999298</v>
+        <v>2.7190607833334299</v>
       </c>
       <c r="D13" s="2">
-        <v>2.8445698000000399</v>
+        <v>2.7286221500000098</v>
       </c>
       <c r="E13" s="2">
-        <v>2.6098971999999701</v>
+        <v>2.56352223333336</v>
       </c>
       <c r="F13" s="2">
-        <v>2.7353607000000002</v>
+        <v>2.91989296666664</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="1"/>
@@ -8795,19 +8818,19 @@
         <v>17000</v>
       </c>
       <c r="B14" s="3">
-        <v>3.3449150000001202</v>
+        <v>2.8577134166666802</v>
       </c>
       <c r="C14" s="2">
-        <v>3.0529510999999698</v>
+        <v>3.0772922666666598</v>
       </c>
       <c r="D14" s="2">
-        <v>4.2412036000000599</v>
+        <v>3.1502399666666498</v>
       </c>
       <c r="E14" s="2">
-        <v>2.99417149999999</v>
+        <v>2.9128057999999601</v>
       </c>
       <c r="F14" s="2">
-        <v>3.3449150000001202</v>
+        <v>3.32174546666662</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="1"/>
@@ -8821,19 +8844,19 @@
         <v>18000</v>
       </c>
       <c r="B15" s="3">
-        <v>3.40162020000025</v>
+        <v>3.20324408333332</v>
       </c>
       <c r="C15" s="2">
-        <v>3.44943740000007</v>
+        <v>3.51721174999996</v>
       </c>
       <c r="D15" s="2">
-        <v>3.6253870999998901</v>
+        <v>3.5464354999999101</v>
       </c>
       <c r="E15" s="2">
-        <v>3.33117489999995</v>
+        <v>3.2378344833333901</v>
       </c>
       <c r="F15" s="2">
-        <v>3.40162020000025</v>
+        <v>3.6998055166667001</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="1"/>
@@ -8847,19 +8870,19 @@
         <v>19000</v>
       </c>
       <c r="B16" s="3">
-        <v>4.11404940000011</v>
+        <v>3.5692949500000002</v>
       </c>
       <c r="C16" s="2">
-        <v>3.81637829999999</v>
+        <v>3.8006664833333099</v>
       </c>
       <c r="D16" s="2">
-        <v>4.1029728000003098</v>
+        <v>3.9288310000000202</v>
       </c>
       <c r="E16" s="2">
-        <v>3.7084792000000499</v>
+        <v>3.6026052166665301</v>
       </c>
       <c r="F16" s="2">
-        <v>4.11404940000011</v>
+        <v>4.2211402500000297</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="1"/>
